--- a/DataMaster.xlsx
+++ b/DataMaster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\young\Dropbox\Michael\Work-Uni-Coding\Youngs Farm Analysis\FOG\Work\R&amp;D\Stirlings to Coast\RiskWise\Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2171A8AF-59E1-462F-B1BC-00EBD105B453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE20ADB-0E83-423F-AFDC-E8E3254FD922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10EDD844-9EC5-4F2C-A4A7-506A3C8B05B2}"/>
+    <workbookView xWindow="-28950" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{10EDD844-9EC5-4F2C-A4A7-506A3C8B05B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -26309,7 +26309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2780" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3321" uniqueCount="39">
   <si>
     <t>Year</t>
   </si>
@@ -26419,10 +26419,13 @@
     <t>N conversion factor</t>
   </si>
   <si>
-    <t>Total available soil N (kg/ha)</t>
+    <t/>
   </si>
   <si>
-    <t/>
+    <t>Pre-seed Total available soil N 0-90cm (kg/ha)</t>
+  </si>
+  <si>
+    <t>Post-harv Total available soil N 0-90cm (kg/ha)</t>
   </si>
 </sst>
 </file>
@@ -26906,15 +26909,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67DB2DCA-317A-42E1-94B7-A557731F58A0}">
-  <dimension ref="A1:AK271"/>
+  <dimension ref="A1:AL271"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>23</v>
       </c>
@@ -26988,10 +26991,13 @@
         <v>34</v>
       </c>
       <c r="X1" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="Y1" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>24</v>
       </c>
@@ -27018,6 +27024,15 @@
       </c>
       <c r="I2" t="s">
         <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>17</v>
@@ -27046,11 +27061,8 @@
         <f>V2/Q2</f>
         <v>0.42955243345323391</v>
       </c>
-      <c r="X2">
-        <v>87.56</v>
-      </c>
     </row>
-    <row r="3" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>25</v>
       </c>
@@ -27077,6 +27089,15 @@
       </c>
       <c r="I3" t="s">
         <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>17</v>
@@ -27105,11 +27126,8 @@
         <f t="shared" ref="W3:W66" si="1">V3/Q3</f>
         <v>0.63609809256787742</v>
       </c>
-      <c r="X3">
-        <v>87.949999999999989</v>
-      </c>
     </row>
-    <row r="4" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>26</v>
       </c>
@@ -27136,6 +27154,15 @@
       </c>
       <c r="I4" t="s">
         <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>17</v>
@@ -27164,11 +27191,8 @@
         <f t="shared" si="1"/>
         <v>3.511876310783788</v>
       </c>
-      <c r="X4">
-        <v>99.81</v>
-      </c>
     </row>
-    <row r="5" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>26</v>
       </c>
@@ -27195,6 +27219,15 @@
       </c>
       <c r="I5" t="s">
         <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
@@ -27223,11 +27256,8 @@
         <f t="shared" si="1"/>
         <v>3.0891089108910892</v>
       </c>
-      <c r="X5">
-        <v>63.650000000000006</v>
-      </c>
     </row>
-    <row r="6" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -27254,6 +27284,15 @@
       </c>
       <c r="I6" t="s">
         <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
@@ -27282,11 +27321,8 @@
         <f t="shared" si="1"/>
         <v>0.50254897830208534</v>
       </c>
-      <c r="X6">
-        <v>121.57999999999998</v>
-      </c>
     </row>
-    <row r="7" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>24</v>
       </c>
@@ -27313,6 +27349,15 @@
       </c>
       <c r="I7" t="s">
         <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" t="s">
+        <v>19</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -27341,11 +27386,8 @@
         <f t="shared" si="1"/>
         <v>0.30844070708440718</v>
       </c>
-      <c r="X7">
-        <v>83.300000000000011</v>
-      </c>
     </row>
-    <row r="8" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -27372,6 +27414,15 @@
       </c>
       <c r="I8" t="s">
         <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" t="s">
+        <v>19</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>17</v>
@@ -27400,11 +27451,8 @@
         <f t="shared" si="1"/>
         <v>2.7192118226600979</v>
       </c>
-      <c r="X8">
-        <v>68.109999999999985</v>
-      </c>
     </row>
-    <row r="9" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>24</v>
       </c>
@@ -27431,6 +27479,15 @@
       </c>
       <c r="I9" t="s">
         <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" t="s">
+        <v>19</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>17</v>
@@ -27459,11 +27516,8 @@
         <f t="shared" si="1"/>
         <v>0.30787927134616377</v>
       </c>
-      <c r="X9">
-        <v>73.850000000000009</v>
-      </c>
     </row>
-    <row r="10" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
@@ -27490,6 +27544,15 @@
       </c>
       <c r="I10" t="s">
         <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" t="s">
+        <v>19</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>17</v>
@@ -27518,11 +27581,8 @@
         <f t="shared" si="1"/>
         <v>0.43866455611078348</v>
       </c>
-      <c r="X10">
-        <v>77.099999999999994</v>
-      </c>
     </row>
-    <row r="11" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>25</v>
       </c>
@@ -27549,6 +27609,15 @@
       </c>
       <c r="I11" t="s">
         <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" t="s">
+        <v>19</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
@@ -27577,11 +27646,8 @@
         <f t="shared" si="1"/>
         <v>0.57682145114207473</v>
       </c>
-      <c r="X11" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="12" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -27608,6 +27674,15 @@
       </c>
       <c r="I12" t="s">
         <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" t="s">
+        <v>19</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
@@ -27636,11 +27711,8 @@
         <f t="shared" si="1"/>
         <v>3.2893465346534656</v>
       </c>
-      <c r="X12" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="13" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>24</v>
       </c>
@@ -27667,6 +27739,15 @@
       </c>
       <c r="I13" t="s">
         <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" t="s">
+        <v>19</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -27695,9 +27776,7 @@
         <f t="shared" si="1"/>
         <v>0.29446952523040959</v>
       </c>
-      <c r="X13" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
@@ -27711,8 +27790,9 @@
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
+      <c r="AL13" s="1"/>
     </row>
-    <row r="14" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>24</v>
       </c>
@@ -27739,6 +27819,15 @@
       </c>
       <c r="I14" t="s">
         <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>19</v>
@@ -27767,16 +27856,13 @@
         <f t="shared" si="1"/>
         <v>0.5655349473146396</v>
       </c>
-      <c r="X14">
-        <v>91.11</v>
-      </c>
-      <c r="AD14" s="4"/>
-      <c r="AH14" s="5"/>
-      <c r="AI14" s="6"/>
-      <c r="AJ14" s="7"/>
+      <c r="AE14" s="4"/>
+      <c r="AI14" s="5"/>
+      <c r="AJ14" s="6"/>
       <c r="AK14" s="7"/>
+      <c r="AL14" s="7"/>
     </row>
-    <row r="15" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -27803,6 +27889,15 @@
       </c>
       <c r="I15" t="s">
         <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>19</v>
@@ -27831,16 +27926,13 @@
         <f t="shared" si="1"/>
         <v>4.0662889818393593</v>
       </c>
-      <c r="X15">
-        <v>54.599999999999994</v>
-      </c>
-      <c r="AD15" s="4"/>
-      <c r="AH15" s="5"/>
-      <c r="AI15" s="6"/>
-      <c r="AJ15" s="7"/>
+      <c r="AE15" s="4"/>
+      <c r="AI15" s="5"/>
+      <c r="AJ15" s="6"/>
       <c r="AK15" s="7"/>
+      <c r="AL15" s="7"/>
     </row>
-    <row r="16" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -27867,6 +27959,15 @@
       </c>
       <c r="I16" t="s">
         <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" t="s">
+        <v>19</v>
       </c>
       <c r="M16" s="4" t="s">
         <v>19</v>
@@ -27895,16 +27996,13 @@
         <f t="shared" si="1"/>
         <v>0.81436715100081447</v>
       </c>
-      <c r="X16">
-        <v>44.74</v>
-      </c>
-      <c r="AD16" s="4"/>
-      <c r="AH16" s="5"/>
-      <c r="AI16" s="6"/>
-      <c r="AJ16" s="7"/>
+      <c r="AE16" s="4"/>
+      <c r="AI16" s="5"/>
+      <c r="AJ16" s="6"/>
       <c r="AK16" s="7"/>
+      <c r="AL16" s="7"/>
     </row>
-    <row r="17" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -27931,6 +28029,15 @@
       </c>
       <c r="I17" t="s">
         <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" t="s">
+        <v>19</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>20</v>
@@ -27959,16 +28066,13 @@
         <f t="shared" si="1"/>
         <v>13.039434229137203</v>
       </c>
-      <c r="X17">
-        <v>103.7</v>
-      </c>
-      <c r="AD17" s="4"/>
-      <c r="AH17" s="5"/>
-      <c r="AI17" s="6"/>
-      <c r="AJ17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AI17" s="5"/>
+      <c r="AJ17" s="6"/>
       <c r="AK17" s="4"/>
+      <c r="AL17" s="4"/>
     </row>
-    <row r="18" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>24</v>
       </c>
@@ -27995,6 +28099,15 @@
       </c>
       <c r="I18" t="s">
         <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" t="s">
+        <v>19</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>20</v>
@@ -28023,16 +28136,13 @@
         <f t="shared" si="1"/>
         <v>11.883360678925037</v>
       </c>
-      <c r="X18">
-        <v>67.28</v>
-      </c>
-      <c r="AD18" s="4"/>
-      <c r="AH18" s="5"/>
-      <c r="AI18" s="6"/>
-      <c r="AJ18" s="8"/>
+      <c r="AE18" s="4"/>
+      <c r="AI18" s="5"/>
+      <c r="AJ18" s="6"/>
       <c r="AK18" s="8"/>
+      <c r="AL18" s="8"/>
     </row>
-    <row r="19" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -28059,6 +28169,15 @@
       </c>
       <c r="I19" t="s">
         <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" t="s">
+        <v>19</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>20</v>
@@ -28087,16 +28206,13 @@
         <f t="shared" si="1"/>
         <v>12.889618104667608</v>
       </c>
-      <c r="X19" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD19" s="4"/>
-      <c r="AH19" s="5"/>
-      <c r="AI19" s="6"/>
-      <c r="AJ19" s="8"/>
+      <c r="AE19" s="4"/>
+      <c r="AI19" s="5"/>
+      <c r="AJ19" s="6"/>
       <c r="AK19" s="8"/>
+      <c r="AL19" s="8"/>
     </row>
-    <row r="20" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -28123,6 +28239,15 @@
       </c>
       <c r="I20" t="s">
         <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" t="s">
+        <v>19</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>20</v>
@@ -28151,16 +28276,13 @@
         <f t="shared" si="1"/>
         <v>10.515190947666195</v>
       </c>
-      <c r="X20" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD20" s="4"/>
-      <c r="AH20" s="5"/>
-      <c r="AI20" s="6"/>
-      <c r="AJ20" s="7"/>
+      <c r="AE20" s="4"/>
+      <c r="AI20" s="5"/>
+      <c r="AJ20" s="6"/>
       <c r="AK20" s="7"/>
+      <c r="AL20" s="7"/>
     </row>
-    <row r="21" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>24</v>
       </c>
@@ -28187,6 +28309,15 @@
       </c>
       <c r="I21" t="s">
         <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" t="s">
+        <v>19</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>20</v>
@@ -28215,16 +28346,13 @@
         <f t="shared" si="1"/>
         <v>10.698772277227722</v>
       </c>
-      <c r="X21" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD21" s="4"/>
-      <c r="AH21" s="5"/>
-      <c r="AI21" s="6"/>
-      <c r="AJ21" s="7"/>
+      <c r="AE21" s="4"/>
+      <c r="AI21" s="5"/>
+      <c r="AJ21" s="6"/>
       <c r="AK21" s="7"/>
+      <c r="AL21" s="7"/>
     </row>
-    <row r="22" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -28251,6 +28379,15 @@
       </c>
       <c r="I22" t="s">
         <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" t="s">
+        <v>19</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>20</v>
@@ -28279,16 +28416,13 @@
         <f t="shared" si="1"/>
         <v>10.052345120226306</v>
       </c>
-      <c r="X22" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD22" s="4"/>
-      <c r="AH22" s="5"/>
-      <c r="AI22" s="6"/>
-      <c r="AJ22" s="7"/>
+      <c r="AE22" s="4"/>
+      <c r="AI22" s="5"/>
+      <c r="AJ22" s="6"/>
       <c r="AK22" s="7"/>
+      <c r="AL22" s="7"/>
     </row>
-    <row r="23" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -28315,6 +28449,15 @@
       </c>
       <c r="I23" t="s">
         <v>15</v>
+      </c>
+      <c r="J23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" t="s">
+        <v>19</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
@@ -28343,11 +28486,8 @@
         <f t="shared" si="1"/>
         <v>1.3560396039603959</v>
       </c>
-      <c r="X23" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="24" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -28374,6 +28514,15 @@
       </c>
       <c r="I24" t="s">
         <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" t="s">
+        <v>19</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -28402,11 +28551,8 @@
         <f t="shared" si="1"/>
         <v>0.36141924222817423</v>
       </c>
-      <c r="X24" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="25" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
@@ -28433,6 +28579,15 @@
       </c>
       <c r="I25" t="s">
         <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" t="s">
+        <v>19</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
@@ -28461,11 +28616,8 @@
         <f t="shared" si="1"/>
         <v>0.21725601131541727</v>
       </c>
-      <c r="X25" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="26" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -28492,6 +28644,15 @@
       </c>
       <c r="I26" t="s">
         <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" t="s">
+        <v>19</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>19</v>
@@ -28520,11 +28681,8 @@
         <f t="shared" si="1"/>
         <v>2.1993459850186694</v>
       </c>
-      <c r="X26">
-        <v>60.53</v>
-      </c>
     </row>
-    <row r="27" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -28551,6 +28709,15 @@
       </c>
       <c r="I27" t="s">
         <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" t="s">
+        <v>19</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>19</v>
@@ -28579,11 +28746,8 @@
         <f t="shared" si="1"/>
         <v>0.6317922344819149</v>
       </c>
-      <c r="X27">
-        <v>61.504999999999995</v>
-      </c>
     </row>
-    <row r="28" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
         <v>24</v>
       </c>
@@ -28610,6 +28774,15 @@
       </c>
       <c r="I28" t="s">
         <v>15</v>
+      </c>
+      <c r="J28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" t="s">
+        <v>19</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>19</v>
@@ -28638,11 +28811,8 @@
         <f t="shared" si="1"/>
         <v>0.29303186672918985</v>
       </c>
-      <c r="X28">
-        <v>52.884999999999998</v>
-      </c>
     </row>
-    <row r="29" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
         <v>24</v>
       </c>
@@ -28669,6 +28839,15 @@
       </c>
       <c r="I29" t="s">
         <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" t="s">
+        <v>19</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>17</v>
@@ -28697,11 +28876,8 @@
         <f t="shared" si="1"/>
         <v>0.2933340041059021</v>
       </c>
-      <c r="X29" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="30" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -28728,6 +28904,15 @@
       </c>
       <c r="I30" t="s">
         <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" t="s">
+        <v>19</v>
       </c>
       <c r="M30" s="4" t="s">
         <v>17</v>
@@ -28756,11 +28941,8 @@
         <f t="shared" si="1"/>
         <v>0.49634273772204807</v>
       </c>
-      <c r="X30" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="31" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
         <v>26</v>
       </c>
@@ -28787,6 +28969,15 @@
       </c>
       <c r="I31" t="s">
         <v>15</v>
+      </c>
+      <c r="J31" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" t="s">
+        <v>19</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>17</v>
@@ -28815,11 +29006,8 @@
         <f t="shared" si="1"/>
         <v>2.7053601911915335</v>
       </c>
-      <c r="X31" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="32" spans="1:37" ht="16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="16" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>24</v>
       </c>
@@ -28846,6 +29034,15 @@
       </c>
       <c r="I32" t="s">
         <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" t="s">
+        <v>19</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>19</v>
@@ -28874,11 +29071,8 @@
         <f t="shared" si="1"/>
         <v>0.58851746145541917</v>
       </c>
-      <c r="X32">
-        <v>74.27</v>
-      </c>
     </row>
-    <row r="33" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
         <v>26</v>
       </c>
@@ -28905,6 +29099,15 @@
       </c>
       <c r="I33" t="s">
         <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" t="s">
+        <v>19</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>19</v>
@@ -28933,11 +29136,8 @@
         <f t="shared" si="1"/>
         <v>5.1508021390374328</v>
       </c>
-      <c r="X33">
-        <v>48.55</v>
-      </c>
     </row>
-    <row r="34" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
         <v>25</v>
       </c>
@@ -28964,6 +29164,15 @@
       </c>
       <c r="I34" t="s">
         <v>15</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" t="s">
+        <v>19</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>19</v>
@@ -28992,11 +29201,8 @@
         <f t="shared" si="1"/>
         <v>0.97373017159113417</v>
       </c>
-      <c r="X34">
-        <v>60.539999999999992</v>
-      </c>
     </row>
-    <row r="35" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
         <v>25</v>
       </c>
@@ -29023,6 +29229,15 @@
       </c>
       <c r="I35" t="s">
         <v>15</v>
+      </c>
+      <c r="J35" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" t="s">
+        <v>19</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>20</v>
@@ -29051,11 +29266,8 @@
         <f t="shared" si="1"/>
         <v>13.17997714285714</v>
       </c>
-      <c r="X35" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="36" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
         <v>24</v>
       </c>
@@ -29082,6 +29294,15 @@
       </c>
       <c r="I36" t="s">
         <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" t="s">
+        <v>19</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>20</v>
@@ -29110,11 +29331,8 @@
         <f t="shared" si="1"/>
         <v>17.696548571428572</v>
       </c>
-      <c r="X36" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="37" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -29141,6 +29359,15 @@
       </c>
       <c r="I37" t="s">
         <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" t="s">
+        <v>19</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>20</v>
@@ -29169,11 +29396,8 @@
         <f t="shared" si="1"/>
         <v>15.113874285714285</v>
       </c>
-      <c r="X37" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="38" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
         <v>26</v>
       </c>
@@ -29200,6 +29424,15 @@
       </c>
       <c r="I38" t="s">
         <v>15</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" t="s">
+        <v>19</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>18</v>
@@ -29228,11 +29461,8 @@
         <f t="shared" si="1"/>
         <v>2.9030399999999994</v>
       </c>
-      <c r="X38" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="39" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
         <v>24</v>
       </c>
@@ -29259,6 +29489,15 @@
       </c>
       <c r="I39" t="s">
         <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" t="s">
+        <v>18</v>
+      </c>
+      <c r="L39" t="s">
+        <v>19</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>18</v>
@@ -29287,11 +29526,8 @@
         <f t="shared" si="1"/>
         <v>0.27866927592954993</v>
       </c>
-      <c r="X39" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="40" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
         <v>25</v>
       </c>
@@ -29318,6 +29554,15 @@
       </c>
       <c r="I40" t="s">
         <v>15</v>
+      </c>
+      <c r="J40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" t="s">
+        <v>19</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>18</v>
@@ -29346,11 +29591,8 @@
         <f t="shared" si="1"/>
         <v>0.55314285714285716</v>
       </c>
-      <c r="X40" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="41" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A41" s="11" t="s">
         <v>26</v>
       </c>
@@ -29377,6 +29619,15 @@
       </c>
       <c r="I41" t="s">
         <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" t="s">
+        <v>19</v>
       </c>
       <c r="M41" s="4" t="s">
         <v>18</v>
@@ -29405,11 +29656,8 @@
         <f t="shared" si="1"/>
         <v>4.0102400000000014</v>
       </c>
-      <c r="X41">
-        <v>80.02000000000001</v>
-      </c>
     </row>
-    <row r="42" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A42" s="11" t="s">
         <v>25</v>
       </c>
@@ -29436,6 +29684,15 @@
       </c>
       <c r="I42" t="s">
         <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" t="s">
+        <v>19</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>18</v>
@@ -29464,11 +29721,8 @@
         <f t="shared" si="1"/>
         <v>0.71703343465045588</v>
       </c>
-      <c r="X42">
-        <v>64.215000000000003</v>
-      </c>
     </row>
-    <row r="43" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
         <v>24</v>
       </c>
@@ -29495,6 +29749,15 @@
       </c>
       <c r="I43" t="s">
         <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" t="s">
+        <v>18</v>
+      </c>
+      <c r="L43" t="s">
+        <v>19</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>18</v>
@@ -29523,11 +29786,8 @@
         <f t="shared" si="1"/>
         <v>0.36336073059360735</v>
       </c>
-      <c r="X43">
-        <v>116.25999999999999</v>
-      </c>
     </row>
-    <row r="44" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A44" s="11" t="s">
         <v>24</v>
       </c>
@@ -29554,6 +29814,15 @@
       </c>
       <c r="I44" t="s">
         <v>15</v>
+      </c>
+      <c r="J44" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" t="s">
+        <v>18</v>
+      </c>
+      <c r="L44" t="s">
+        <v>19</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>17</v>
@@ -29582,11 +29851,8 @@
         <f t="shared" si="1"/>
         <v>0.49591287998760059</v>
       </c>
-      <c r="X44" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="45" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A45" s="11" t="s">
         <v>25</v>
       </c>
@@ -29613,6 +29879,15 @@
       </c>
       <c r="I45" t="s">
         <v>15</v>
+      </c>
+      <c r="J45" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" t="s">
+        <v>18</v>
+      </c>
+      <c r="L45" t="s">
+        <v>19</v>
       </c>
       <c r="M45" s="4" t="s">
         <v>17</v>
@@ -29641,11 +29916,8 @@
         <f t="shared" si="1"/>
         <v>0.64733542319749215</v>
       </c>
-      <c r="X45" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="46" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
         <v>26</v>
       </c>
@@ -29672,6 +29944,15 @@
       </c>
       <c r="I46" t="s">
         <v>15</v>
+      </c>
+      <c r="J46" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" t="s">
+        <v>18</v>
+      </c>
+      <c r="L46" t="s">
+        <v>19</v>
       </c>
       <c r="M46" s="4" t="s">
         <v>17</v>
@@ -29700,11 +29981,8 @@
         <f t="shared" si="1"/>
         <v>5.3205911330049256</v>
       </c>
-      <c r="X46" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="47" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
         <v>25</v>
       </c>
@@ -29731,6 +30009,15 @@
       </c>
       <c r="I47" t="s">
         <v>15</v>
+      </c>
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" t="s">
+        <v>19</v>
       </c>
       <c r="M47" s="4" t="s">
         <v>17</v>
@@ -29759,11 +30046,8 @@
         <f t="shared" si="1"/>
         <v>0.73122854157336914</v>
       </c>
-      <c r="X47" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="48" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
         <v>26</v>
       </c>
@@ -29790,6 +30074,15 @@
       </c>
       <c r="I48" t="s">
         <v>15</v>
+      </c>
+      <c r="J48" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" t="s">
+        <v>19</v>
       </c>
       <c r="M48" s="4" t="s">
         <v>17</v>
@@ -29818,11 +30111,8 @@
         <f t="shared" si="1"/>
         <v>3.519211822660099</v>
       </c>
-      <c r="X48" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="49" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
         <v>24</v>
       </c>
@@ -29849,6 +30139,15 @@
       </c>
       <c r="I49" t="s">
         <v>15</v>
+      </c>
+      <c r="J49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" t="s">
+        <v>19</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>17</v>
@@ -29877,11 +30176,8 @@
         <f t="shared" si="1"/>
         <v>0.41923810422324509</v>
       </c>
-      <c r="X49">
-        <v>74.319999999999993</v>
-      </c>
     </row>
-    <row r="50" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
         <v>24</v>
       </c>
@@ -29908,6 +30204,15 @@
       </c>
       <c r="I50" t="s">
         <v>15</v>
+      </c>
+      <c r="J50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" t="s">
+        <v>19</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>19</v>
@@ -29936,11 +30241,8 @@
         <f t="shared" si="1"/>
         <v>0.36772326142246475</v>
       </c>
-      <c r="X50" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="51" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
         <v>26</v>
       </c>
@@ -29967,6 +30269,15 @@
       </c>
       <c r="I51" t="s">
         <v>15</v>
+      </c>
+      <c r="J51" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" t="s">
+        <v>19</v>
       </c>
       <c r="M51" s="4" t="s">
         <v>19</v>
@@ -29995,11 +30306,8 @@
         <f t="shared" si="1"/>
         <v>2.6108479755538574</v>
       </c>
-      <c r="X51" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="52" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
         <v>25</v>
       </c>
@@ -30026,6 +30334,15 @@
       </c>
       <c r="I52" t="s">
         <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" t="s">
+        <v>19</v>
       </c>
       <c r="M52" s="4" t="s">
         <v>19</v>
@@ -30054,11 +30371,8 @@
         <f t="shared" si="1"/>
         <v>0.7338729798622845</v>
       </c>
-      <c r="X52" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="53" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
         <v>25</v>
       </c>
@@ -30085,6 +30399,15 @@
       </c>
       <c r="I53" t="s">
         <v>15</v>
+      </c>
+      <c r="J53" t="s">
+        <v>17</v>
+      </c>
+      <c r="K53" t="s">
+        <v>18</v>
+      </c>
+      <c r="L53" t="s">
+        <v>19</v>
       </c>
       <c r="M53" s="4" t="s">
         <v>18</v>
@@ -30113,11 +30436,8 @@
         <f t="shared" si="1"/>
         <v>0.41889361702127659</v>
       </c>
-      <c r="X53" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="54" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A54" s="11" t="s">
         <v>26</v>
       </c>
@@ -30144,6 +30464,15 @@
       </c>
       <c r="I54" t="s">
         <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54" t="s">
+        <v>18</v>
+      </c>
+      <c r="L54" t="s">
+        <v>19</v>
       </c>
       <c r="M54" s="4" t="s">
         <v>18</v>
@@ -30172,11 +30501,8 @@
         <f t="shared" si="1"/>
         <v>1.0649600000000001</v>
       </c>
-      <c r="X54" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="55" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A55" s="11" t="s">
         <v>24</v>
       </c>
@@ -30203,6 +30529,15 @@
       </c>
       <c r="I55" t="s">
         <v>15</v>
+      </c>
+      <c r="J55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" t="s">
+        <v>18</v>
+      </c>
+      <c r="L55" t="s">
+        <v>19</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>18</v>
@@ -30231,11 +30566,8 @@
         <f t="shared" si="1"/>
         <v>0.24205609915198964</v>
       </c>
-      <c r="X55" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="56" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A56" s="11" t="s">
         <v>26</v>
       </c>
@@ -30262,6 +30594,15 @@
       </c>
       <c r="I56" t="s">
         <v>15</v>
+      </c>
+      <c r="J56" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56" t="s">
+        <v>18</v>
+      </c>
+      <c r="L56" t="s">
+        <v>19</v>
       </c>
       <c r="M56" s="4" t="s">
         <v>20</v>
@@ -30290,11 +30631,8 @@
         <f t="shared" si="1"/>
         <v>13.8432</v>
       </c>
-      <c r="X56">
-        <v>57.89</v>
-      </c>
     </row>
-    <row r="57" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
         <v>24</v>
       </c>
@@ -30321,6 +30659,15 @@
       </c>
       <c r="I57" t="s">
         <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" t="s">
+        <v>19</v>
       </c>
       <c r="M57" s="4" t="s">
         <v>20</v>
@@ -30349,11 +30696,8 @@
         <f t="shared" si="1"/>
         <v>14.68544</v>
       </c>
-      <c r="X57">
-        <v>62.320000000000007</v>
-      </c>
     </row>
-    <row r="58" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A58" s="11" t="s">
         <v>25</v>
       </c>
@@ -30380,6 +30724,15 @@
       </c>
       <c r="I58" t="s">
         <v>15</v>
+      </c>
+      <c r="J58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58" t="s">
+        <v>18</v>
+      </c>
+      <c r="L58" t="s">
+        <v>19</v>
       </c>
       <c r="M58" s="4" t="s">
         <v>20</v>
@@ -30408,11 +30761,8 @@
         <f t="shared" si="1"/>
         <v>14.508617142857142</v>
       </c>
-      <c r="X58">
-        <v>55.36</v>
-      </c>
     </row>
-    <row r="59" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A59" s="11" t="s">
         <v>25</v>
       </c>
@@ -30439,6 +30789,15 @@
       </c>
       <c r="I59" t="s">
         <v>15</v>
+      </c>
+      <c r="J59" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" t="s">
+        <v>18</v>
+      </c>
+      <c r="L59" t="s">
+        <v>19</v>
       </c>
       <c r="M59" s="4" t="s">
         <v>17</v>
@@ -30467,11 +30826,8 @@
         <f t="shared" si="1"/>
         <v>0.71367617057272226</v>
       </c>
-      <c r="X59" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="60" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A60" s="11" t="s">
         <v>24</v>
       </c>
@@ -30498,6 +30854,15 @@
       </c>
       <c r="I60" t="s">
         <v>15</v>
+      </c>
+      <c r="J60" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" t="s">
+        <v>18</v>
+      </c>
+      <c r="L60" t="s">
+        <v>19</v>
       </c>
       <c r="M60" s="4" t="s">
         <v>17</v>
@@ -30526,11 +30891,8 @@
         <f t="shared" si="1"/>
         <v>0.33048728713618575</v>
       </c>
-      <c r="X60" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="61" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A61" s="11" t="s">
         <v>26</v>
       </c>
@@ -30557,6 +30919,15 @@
       </c>
       <c r="I61" t="s">
         <v>15</v>
+      </c>
+      <c r="J61" t="s">
+        <v>17</v>
+      </c>
+      <c r="K61" t="s">
+        <v>18</v>
+      </c>
+      <c r="L61" t="s">
+        <v>19</v>
       </c>
       <c r="M61" s="4" t="s">
         <v>17</v>
@@ -30585,11 +30956,8 @@
         <f t="shared" si="1"/>
         <v>2.1990147783251235</v>
       </c>
-      <c r="X61" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="62" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A62" s="11" t="s">
         <v>26</v>
       </c>
@@ -30616,6 +30984,15 @@
       </c>
       <c r="I62" t="s">
         <v>15</v>
+      </c>
+      <c r="J62" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62" t="s">
+        <v>18</v>
+      </c>
+      <c r="L62" t="s">
+        <v>19</v>
       </c>
       <c r="M62" s="4" t="s">
         <v>19</v>
@@ -30644,11 +31021,8 @@
         <f t="shared" si="1"/>
         <v>5.2013241660300489</v>
       </c>
-      <c r="X62">
-        <v>39.594999999999999</v>
-      </c>
     </row>
-    <row r="63" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A63" s="11" t="s">
         <v>25</v>
       </c>
@@ -30675,6 +31049,15 @@
       </c>
       <c r="I63" t="s">
         <v>15</v>
+      </c>
+      <c r="J63" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63" t="s">
+        <v>18</v>
+      </c>
+      <c r="L63" t="s">
+        <v>19</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>19</v>
@@ -30703,11 +31086,8 @@
         <f t="shared" si="1"/>
         <v>0.8020232886543045</v>
       </c>
-      <c r="X63">
-        <v>55.660000000000004</v>
-      </c>
     </row>
-    <row r="64" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A64" s="11" t="s">
         <v>24</v>
       </c>
@@ -30734,6 +31114,15 @@
       </c>
       <c r="I64" t="s">
         <v>15</v>
+      </c>
+      <c r="J64" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64" t="s">
+        <v>18</v>
+      </c>
+      <c r="L64" t="s">
+        <v>19</v>
       </c>
       <c r="M64" s="4" t="s">
         <v>19</v>
@@ -30762,11 +31151,8 @@
         <f t="shared" si="1"/>
         <v>0.52671236384119624</v>
       </c>
-      <c r="X64">
-        <v>68.160000000000011</v>
-      </c>
     </row>
-    <row r="65" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A65" s="11" t="s">
         <v>25</v>
       </c>
@@ -30793,6 +31179,15 @@
       </c>
       <c r="I65" t="s">
         <v>15</v>
+      </c>
+      <c r="J65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65" t="s">
+        <v>18</v>
+      </c>
+      <c r="L65" t="s">
+        <v>19</v>
       </c>
       <c r="M65" s="4" t="s">
         <v>17</v>
@@ -30821,11 +31216,8 @@
         <f t="shared" si="1"/>
         <v>0.53297755883962783</v>
       </c>
-      <c r="X65">
-        <v>73.209999999999994</v>
-      </c>
     </row>
-    <row r="66" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A66" s="11" t="s">
         <v>24</v>
       </c>
@@ -30852,6 +31244,15 @@
       </c>
       <c r="I66" t="s">
         <v>15</v>
+      </c>
+      <c r="J66" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" t="s">
+        <v>18</v>
+      </c>
+      <c r="L66" t="s">
+        <v>19</v>
       </c>
       <c r="M66" s="4" t="s">
         <v>17</v>
@@ -30880,11 +31281,8 @@
         <f t="shared" si="1"/>
         <v>0.35446415936061676</v>
       </c>
-      <c r="X66">
-        <v>60.019999999999996</v>
-      </c>
     </row>
-    <row r="67" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A67" s="11" t="s">
         <v>26</v>
       </c>
@@ -30911,6 +31309,15 @@
       </c>
       <c r="I67" t="s">
         <v>15</v>
+      </c>
+      <c r="J67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K67" t="s">
+        <v>18</v>
+      </c>
+      <c r="L67" t="s">
+        <v>19</v>
       </c>
       <c r="M67" s="4" t="s">
         <v>17</v>
@@ -30939,11 +31346,8 @@
         <f t="shared" ref="W67:W130" si="3">V67/Q67</f>
         <v>3.8270935960591137</v>
       </c>
-      <c r="X67">
-        <v>51.97</v>
-      </c>
     </row>
-    <row r="68" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A68" s="11" t="s">
         <v>24</v>
       </c>
@@ -30970,6 +31374,15 @@
       </c>
       <c r="I68" t="s">
         <v>15</v>
+      </c>
+      <c r="J68" t="s">
+        <v>17</v>
+      </c>
+      <c r="K68" t="s">
+        <v>18</v>
+      </c>
+      <c r="L68" t="s">
+        <v>19</v>
       </c>
       <c r="M68" s="4" t="s">
         <v>17</v>
@@ -30998,11 +31411,8 @@
         <f t="shared" si="3"/>
         <v>0.45709703287890951</v>
       </c>
-      <c r="X68">
-        <v>45.96</v>
-      </c>
     </row>
-    <row r="69" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A69" s="11" t="s">
         <v>26</v>
       </c>
@@ -31029,6 +31439,15 @@
       </c>
       <c r="I69" t="s">
         <v>15</v>
+      </c>
+      <c r="J69" t="s">
+        <v>17</v>
+      </c>
+      <c r="K69" t="s">
+        <v>18</v>
+      </c>
+      <c r="L69" t="s">
+        <v>19</v>
       </c>
       <c r="M69" s="4" t="s">
         <v>17</v>
@@ -31057,11 +31476,8 @@
         <f t="shared" si="3"/>
         <v>3.3857142857142852</v>
       </c>
-      <c r="X69">
-        <v>40.18</v>
-      </c>
     </row>
-    <row r="70" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A70" s="11" t="s">
         <v>25</v>
       </c>
@@ -31088,6 +31504,15 @@
       </c>
       <c r="I70" t="s">
         <v>15</v>
+      </c>
+      <c r="J70" t="s">
+        <v>17</v>
+      </c>
+      <c r="K70" t="s">
+        <v>18</v>
+      </c>
+      <c r="L70" t="s">
+        <v>19</v>
       </c>
       <c r="M70" s="4" t="s">
         <v>17</v>
@@ -31116,11 +31541,8 @@
         <f t="shared" si="3"/>
         <v>0.74137931034482751</v>
       </c>
-      <c r="X70">
-        <v>35.770000000000003</v>
-      </c>
     </row>
-    <row r="71" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
         <v>26</v>
       </c>
@@ -31147,6 +31569,15 @@
       </c>
       <c r="I71" t="s">
         <v>15</v>
+      </c>
+      <c r="J71" t="s">
+        <v>17</v>
+      </c>
+      <c r="K71" t="s">
+        <v>18</v>
+      </c>
+      <c r="L71" t="s">
+        <v>19</v>
       </c>
       <c r="M71" s="4" t="s">
         <v>20</v>
@@ -31175,11 +31606,8 @@
         <f t="shared" si="3"/>
         <v>13.742537142857142</v>
       </c>
-      <c r="X71">
-        <v>33.69</v>
-      </c>
     </row>
-    <row r="72" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A72" s="11" t="s">
         <v>24</v>
       </c>
@@ -31206,6 +31634,15 @@
       </c>
       <c r="I72" t="s">
         <v>15</v>
+      </c>
+      <c r="J72" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" t="s">
+        <v>18</v>
+      </c>
+      <c r="L72" t="s">
+        <v>19</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>20</v>
@@ -31234,11 +31671,8 @@
         <f t="shared" si="3"/>
         <v>15.4816</v>
       </c>
-      <c r="X72">
-        <v>51.42</v>
-      </c>
     </row>
-    <row r="73" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A73" s="11" t="s">
         <v>25</v>
       </c>
@@ -31265,6 +31699,15 @@
       </c>
       <c r="I73" t="s">
         <v>15</v>
+      </c>
+      <c r="J73" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73" t="s">
+        <v>18</v>
+      </c>
+      <c r="L73" t="s">
+        <v>19</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>20</v>
@@ -31293,11 +31736,8 @@
         <f t="shared" si="3"/>
         <v>14.712960000000004</v>
       </c>
-      <c r="X73">
-        <v>80.199999999999989</v>
-      </c>
     </row>
-    <row r="74" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A74" s="11" t="s">
         <v>24</v>
       </c>
@@ -31324,6 +31764,15 @@
       </c>
       <c r="I74" t="s">
         <v>15</v>
+      </c>
+      <c r="J74" t="s">
+        <v>17</v>
+      </c>
+      <c r="K74" t="s">
+        <v>18</v>
+      </c>
+      <c r="L74" t="s">
+        <v>19</v>
       </c>
       <c r="M74" s="4" t="s">
         <v>18</v>
@@ -31352,11 +31801,8 @@
         <f t="shared" si="3"/>
         <v>0.36292759295499027</v>
       </c>
-      <c r="X74" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="75" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A75" s="11" t="s">
         <v>25</v>
       </c>
@@ -31383,6 +31829,15 @@
       </c>
       <c r="I75" t="s">
         <v>15</v>
+      </c>
+      <c r="J75" t="s">
+        <v>17</v>
+      </c>
+      <c r="K75" t="s">
+        <v>18</v>
+      </c>
+      <c r="L75" t="s">
+        <v>19</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>18</v>
@@ -31411,11 +31866,8 @@
         <f t="shared" si="3"/>
         <v>0.72680851063829777</v>
       </c>
-      <c r="X75" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="76" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A76" s="11" t="s">
         <v>26</v>
       </c>
@@ -31442,6 +31894,15 @@
       </c>
       <c r="I76" t="s">
         <v>15</v>
+      </c>
+      <c r="J76" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76" t="s">
+        <v>18</v>
+      </c>
+      <c r="L76" t="s">
+        <v>19</v>
       </c>
       <c r="M76" s="4" t="s">
         <v>18</v>
@@ -31470,11 +31931,8 @@
         <f t="shared" si="3"/>
         <v>4.1119085714285717</v>
       </c>
-      <c r="X76" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="77" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A77" s="11" t="s">
         <v>24</v>
       </c>
@@ -31501,6 +31959,15 @@
       </c>
       <c r="I77" t="s">
         <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>17</v>
+      </c>
+      <c r="K77" t="s">
+        <v>18</v>
+      </c>
+      <c r="L77" t="s">
+        <v>19</v>
       </c>
       <c r="M77" s="4" t="s">
         <v>18</v>
@@ -31529,11 +31996,8 @@
         <f t="shared" si="3"/>
         <v>0.32521852576647092</v>
       </c>
-      <c r="X77">
-        <v>104.03</v>
-      </c>
     </row>
-    <row r="78" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A78" s="11" t="s">
         <v>26</v>
       </c>
@@ -31560,6 +32024,15 @@
       </c>
       <c r="I78" t="s">
         <v>15</v>
+      </c>
+      <c r="J78" t="s">
+        <v>17</v>
+      </c>
+      <c r="K78" t="s">
+        <v>18</v>
+      </c>
+      <c r="L78" t="s">
+        <v>19</v>
       </c>
       <c r="M78" s="4" t="s">
         <v>18</v>
@@ -31588,11 +32061,8 @@
         <f t="shared" si="3"/>
         <v>3.3737142857142848</v>
       </c>
-      <c r="X78">
-        <v>23.725000000000001</v>
-      </c>
     </row>
-    <row r="79" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A79" s="11" t="s">
         <v>25</v>
       </c>
@@ -31619,6 +32089,15 @@
       </c>
       <c r="I79" t="s">
         <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79" t="s">
+        <v>18</v>
+      </c>
+      <c r="L79" t="s">
+        <v>19</v>
       </c>
       <c r="M79" s="4" t="s">
         <v>18</v>
@@ -31647,11 +32126,8 @@
         <f t="shared" si="3"/>
         <v>0.54164133738601816</v>
       </c>
-      <c r="X79">
-        <v>117.05</v>
-      </c>
     </row>
-    <row r="80" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:23" ht="16" x14ac:dyDescent="0.35">
       <c r="A80" s="11" t="s">
         <v>26</v>
       </c>
@@ -31678,6 +32154,15 @@
       </c>
       <c r="I80" t="s">
         <v>15</v>
+      </c>
+      <c r="J80" t="s">
+        <v>17</v>
+      </c>
+      <c r="K80" t="s">
+        <v>18</v>
+      </c>
+      <c r="L80" t="s">
+        <v>19</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>19</v>
@@ -31706,11 +32191,8 @@
         <f t="shared" si="3"/>
         <v>2.7807486631016043</v>
       </c>
-      <c r="X80" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="81" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A81" s="11" t="s">
         <v>25</v>
       </c>
@@ -31737,6 +32219,15 @@
       </c>
       <c r="I81" t="s">
         <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81" t="s">
+        <v>18</v>
+      </c>
+      <c r="L81" t="s">
+        <v>19</v>
       </c>
       <c r="M81" s="4" t="s">
         <v>19</v>
@@ -31765,11 +32256,8 @@
         <f t="shared" si="3"/>
         <v>0.61067769623919355</v>
       </c>
-      <c r="X81" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="82" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A82" s="11" t="s">
         <v>24</v>
       </c>
@@ -31796,6 +32284,15 @@
       </c>
       <c r="I82" t="s">
         <v>15</v>
+      </c>
+      <c r="J82" t="s">
+        <v>17</v>
+      </c>
+      <c r="K82" t="s">
+        <v>18</v>
+      </c>
+      <c r="L82" t="s">
+        <v>19</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>19</v>
@@ -31824,11 +32321,8 @@
         <f t="shared" si="3"/>
         <v>0.43152791523275152</v>
       </c>
-      <c r="X82" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="83" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A83" s="11" t="s">
         <v>25</v>
       </c>
@@ -31855,6 +32349,15 @@
       </c>
       <c r="I83" t="s">
         <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83" t="s">
+        <v>18</v>
+      </c>
+      <c r="L83" t="s">
+        <v>19</v>
       </c>
       <c r="M83" s="4" t="s">
         <v>18</v>
@@ -31883,11 +32386,8 @@
         <f t="shared" si="3"/>
         <v>0.51997568389057758</v>
       </c>
-      <c r="X83" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="84" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A84" s="11" t="s">
         <v>24</v>
       </c>
@@ -31914,6 +32414,15 @@
       </c>
       <c r="I84" t="s">
         <v>15</v>
+      </c>
+      <c r="J84" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84" t="s">
+        <v>18</v>
+      </c>
+      <c r="L84" t="s">
+        <v>19</v>
       </c>
       <c r="M84" s="4" t="s">
         <v>18</v>
@@ -31942,11 +32451,8 @@
         <f t="shared" si="3"/>
         <v>0.23452054794520555</v>
       </c>
-      <c r="X84" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="85" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A85" s="11" t="s">
         <v>26</v>
       </c>
@@ -31973,6 +32479,15 @@
       </c>
       <c r="I85" t="s">
         <v>15</v>
+      </c>
+      <c r="J85" t="s">
+        <v>17</v>
+      </c>
+      <c r="K85" t="s">
+        <v>18</v>
+      </c>
+      <c r="L85" t="s">
+        <v>19</v>
       </c>
       <c r="M85" s="4" t="s">
         <v>18</v>
@@ -32001,11 +32516,8 @@
         <f t="shared" si="3"/>
         <v>2.5677714285714286</v>
       </c>
-      <c r="X85" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="86" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A86" s="11" t="s">
         <v>24</v>
       </c>
@@ -32032,6 +32544,15 @@
       </c>
       <c r="I86" t="s">
         <v>15</v>
+      </c>
+      <c r="J86" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86" t="s">
+        <v>18</v>
+      </c>
+      <c r="L86" t="s">
+        <v>19</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>17</v>
@@ -32060,11 +32581,8 @@
         <f t="shared" si="3"/>
         <v>0.40972283059173953</v>
       </c>
-      <c r="X86">
-        <v>42.224999999999994</v>
-      </c>
     </row>
-    <row r="87" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A87" s="11" t="s">
         <v>25</v>
       </c>
@@ -32091,6 +32609,15 @@
       </c>
       <c r="I87" t="s">
         <v>15</v>
+      </c>
+      <c r="J87" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" t="s">
+        <v>18</v>
+      </c>
+      <c r="L87" t="s">
+        <v>19</v>
       </c>
       <c r="M87" s="4" t="s">
         <v>17</v>
@@ -32119,11 +32646,8 @@
         <f t="shared" si="3"/>
         <v>0.74389212320246789</v>
       </c>
-      <c r="X87">
-        <v>26.91</v>
-      </c>
     </row>
-    <row r="88" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A88" s="11" t="s">
         <v>26</v>
       </c>
@@ -32150,6 +32674,15 @@
       </c>
       <c r="I88" t="s">
         <v>15</v>
+      </c>
+      <c r="J88" t="s">
+        <v>17</v>
+      </c>
+      <c r="K88" t="s">
+        <v>18</v>
+      </c>
+      <c r="L88" t="s">
+        <v>19</v>
       </c>
       <c r="M88" s="4" t="s">
         <v>17</v>
@@ -32178,11 +32711,8 @@
         <f t="shared" si="3"/>
         <v>3.626403940886699</v>
       </c>
-      <c r="X88">
-        <v>24.055</v>
-      </c>
     </row>
-    <row r="89" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A89" s="11" t="s">
         <v>25</v>
       </c>
@@ -32209,6 +32739,15 @@
       </c>
       <c r="I89" t="s">
         <v>15</v>
+      </c>
+      <c r="J89" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89" t="s">
+        <v>18</v>
+      </c>
+      <c r="L89" t="s">
+        <v>19</v>
       </c>
       <c r="M89" s="4" t="s">
         <v>20</v>
@@ -32237,11 +32776,8 @@
         <f t="shared" si="3"/>
         <v>14.570697142857142</v>
       </c>
-      <c r="X89" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="90" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A90" s="11" t="s">
         <v>24</v>
       </c>
@@ -32268,6 +32804,15 @@
       </c>
       <c r="I90" t="s">
         <v>15</v>
+      </c>
+      <c r="J90" t="s">
+        <v>17</v>
+      </c>
+      <c r="K90" t="s">
+        <v>18</v>
+      </c>
+      <c r="L90" t="s">
+        <v>19</v>
       </c>
       <c r="M90" s="4" t="s">
         <v>20</v>
@@ -32296,11 +32841,8 @@
         <f t="shared" si="3"/>
         <v>13.071999999999997</v>
       </c>
-      <c r="X90" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="91" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A91" s="11" t="s">
         <v>26</v>
       </c>
@@ -32327,6 +32869,15 @@
       </c>
       <c r="I91" t="s">
         <v>15</v>
+      </c>
+      <c r="J91" t="s">
+        <v>17</v>
+      </c>
+      <c r="K91" t="s">
+        <v>18</v>
+      </c>
+      <c r="L91" t="s">
+        <v>19</v>
       </c>
       <c r="M91" s="4" t="s">
         <v>20</v>
@@ -32355,11 +32906,8 @@
         <f t="shared" si="3"/>
         <v>14.762331428571429</v>
       </c>
-      <c r="X91" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="92" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A92" s="11" t="s">
         <v>24</v>
       </c>
@@ -32386,6 +32934,12 @@
       </c>
       <c r="I92" t="s">
         <v>11</v>
+      </c>
+      <c r="J92" t="s">
+        <v>18</v>
+      </c>
+      <c r="K92" t="s">
+        <v>19</v>
       </c>
       <c r="L92" s="4" t="s">
         <v>17</v>
@@ -32421,10 +32975,13 @@
         <v>0.26694663378057742</v>
       </c>
       <c r="X92">
-        <v>144.05000000000001</v>
+        <v>87.56</v>
+      </c>
+      <c r="Y92">
+        <v>120.05</v>
       </c>
     </row>
-    <row r="93" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A93" s="11" t="s">
         <v>25</v>
       </c>
@@ -32451,6 +33008,12 @@
       </c>
       <c r="I93" t="s">
         <v>11</v>
+      </c>
+      <c r="J93" t="s">
+        <v>18</v>
+      </c>
+      <c r="K93" t="s">
+        <v>19</v>
       </c>
       <c r="L93" s="4" t="s">
         <v>17</v>
@@ -32486,10 +33049,13 @@
         <v>0.75813964375160914</v>
       </c>
       <c r="X93">
-        <v>61.45</v>
+        <v>87.949999999999989</v>
+      </c>
+      <c r="Y93">
+        <v>49.45</v>
       </c>
     </row>
-    <row r="94" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A94" s="11" t="s">
         <v>26</v>
       </c>
@@ -32516,6 +33082,12 @@
       </c>
       <c r="I94" t="s">
         <v>11</v>
+      </c>
+      <c r="J94" t="s">
+        <v>18</v>
+      </c>
+      <c r="K94" t="s">
+        <v>19</v>
       </c>
       <c r="L94" s="4" t="s">
         <v>17</v>
@@ -32551,10 +33123,13 @@
         <v>5.3333333333333321</v>
       </c>
       <c r="X94">
-        <v>97.5</v>
+        <v>99.81</v>
+      </c>
+      <c r="Y94">
+        <v>85.5</v>
       </c>
     </row>
-    <row r="95" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A95" s="11" t="s">
         <v>26</v>
       </c>
@@ -32581,6 +33156,12 @@
       </c>
       <c r="I95" t="s">
         <v>11</v>
+      </c>
+      <c r="J95" t="s">
+        <v>18</v>
+      </c>
+      <c r="K95" t="s">
+        <v>19</v>
       </c>
       <c r="L95" s="4" t="s">
         <v>18</v>
@@ -32616,10 +33197,13 @@
         <v>5.1252873563218388</v>
       </c>
       <c r="X95">
-        <v>83.2</v>
+        <v>63.650000000000006</v>
+      </c>
+      <c r="Y95">
+        <v>65.2</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A96" s="11" t="s">
         <v>25</v>
       </c>
@@ -32646,6 +33230,12 @@
       </c>
       <c r="I96" t="s">
         <v>11</v>
+      </c>
+      <c r="J96" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96" t="s">
+        <v>19</v>
       </c>
       <c r="L96" s="4" t="s">
         <v>18</v>
@@ -32681,10 +33271,13 @@
         <v>0.72801772514416174</v>
       </c>
       <c r="X96">
-        <v>115.65</v>
+        <v>121.57999999999998</v>
+      </c>
+      <c r="Y96">
+        <v>94.65</v>
       </c>
     </row>
-    <row r="97" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A97" s="11" t="s">
         <v>24</v>
       </c>
@@ -32711,6 +33304,12 @@
       </c>
       <c r="I97" t="s">
         <v>11</v>
+      </c>
+      <c r="J97" t="s">
+        <v>18</v>
+      </c>
+      <c r="K97" t="s">
+        <v>19</v>
       </c>
       <c r="L97" s="4" t="s">
         <v>18</v>
@@ -32746,10 +33345,13 @@
         <v>0.30268723367454442</v>
       </c>
       <c r="X97">
-        <v>130.19999999999999</v>
+        <v>83.300000000000011</v>
+      </c>
+      <c r="Y97">
+        <v>112.2</v>
       </c>
     </row>
-    <row r="98" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A98" s="11" t="s">
         <v>26</v>
       </c>
@@ -32776,6 +33378,12 @@
       </c>
       <c r="I98" t="s">
         <v>11</v>
+      </c>
+      <c r="J98" t="s">
+        <v>18</v>
+      </c>
+      <c r="K98" t="s">
+        <v>19</v>
       </c>
       <c r="L98" s="4" t="s">
         <v>17</v>
@@ -32811,10 +33419,13 @@
         <v>0</v>
       </c>
       <c r="X98">
-        <v>98.5</v>
+        <v>68.109999999999985</v>
+      </c>
+      <c r="Y98">
+        <v>80.5</v>
       </c>
     </row>
-    <row r="99" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A99" s="11" t="s">
         <v>24</v>
       </c>
@@ -32841,6 +33452,12 @@
       </c>
       <c r="I99" t="s">
         <v>11</v>
+      </c>
+      <c r="J99" t="s">
+        <v>18</v>
+      </c>
+      <c r="K99" t="s">
+        <v>19</v>
       </c>
       <c r="L99" s="4" t="s">
         <v>17</v>
@@ -32876,10 +33493,13 @@
         <v>0.22161339421613396</v>
       </c>
       <c r="X99">
-        <v>107.4</v>
+        <v>73.850000000000009</v>
+      </c>
+      <c r="Y99">
+        <v>95.4</v>
       </c>
     </row>
-    <row r="100" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A100" s="11" t="s">
         <v>25</v>
       </c>
@@ -32906,6 +33526,12 @@
       </c>
       <c r="I100" t="s">
         <v>11</v>
+      </c>
+      <c r="J100" t="s">
+        <v>18</v>
+      </c>
+      <c r="K100" t="s">
+        <v>19</v>
       </c>
       <c r="L100" s="4" t="s">
         <v>17</v>
@@ -32941,10 +33567,13 @@
         <v>0</v>
       </c>
       <c r="X100">
-        <v>155.5</v>
+        <v>77.099999999999994</v>
+      </c>
+      <c r="Y100">
+        <v>128.5</v>
       </c>
     </row>
-    <row r="101" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A101" s="11" t="s">
         <v>25</v>
       </c>
@@ -32971,6 +33600,12 @@
       </c>
       <c r="I101" t="s">
         <v>11</v>
+      </c>
+      <c r="J101" t="s">
+        <v>18</v>
+      </c>
+      <c r="K101" t="s">
+        <v>19</v>
       </c>
       <c r="L101" s="4" t="s">
         <v>18</v>
@@ -33005,11 +33640,14 @@
         <f t="shared" si="3"/>
         <v>1.044011115312363</v>
       </c>
-      <c r="X101">
-        <v>89.15</v>
+      <c r="X101" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y101">
+        <v>71.150000000000006</v>
       </c>
     </row>
-    <row r="102" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A102" s="11" t="s">
         <v>26</v>
       </c>
@@ -33036,6 +33674,12 @@
       </c>
       <c r="I102" t="s">
         <v>11</v>
+      </c>
+      <c r="J102" t="s">
+        <v>18</v>
+      </c>
+      <c r="K102" t="s">
+        <v>19</v>
       </c>
       <c r="L102" s="4" t="s">
         <v>18</v>
@@ -33070,11 +33714,14 @@
         <f t="shared" si="3"/>
         <v>6.5133689839572186</v>
       </c>
-      <c r="X102">
-        <v>34.549999999999997</v>
+      <c r="X102" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y102">
+        <v>28.55</v>
       </c>
     </row>
-    <row r="103" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A103" s="11" t="s">
         <v>24</v>
       </c>
@@ -33101,6 +33748,12 @@
       </c>
       <c r="I103" t="s">
         <v>11</v>
+      </c>
+      <c r="J103" t="s">
+        <v>18</v>
+      </c>
+      <c r="K103" t="s">
+        <v>19</v>
       </c>
       <c r="L103" s="4" t="s">
         <v>18</v>
@@ -33135,11 +33788,14 @@
         <f t="shared" si="3"/>
         <v>0.66781925637643025</v>
       </c>
-      <c r="X103">
-        <v>156.25</v>
+      <c r="X103" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y103">
+        <v>141.25</v>
       </c>
     </row>
-    <row r="104" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A104" s="11" t="s">
         <v>24</v>
       </c>
@@ -33166,6 +33822,12 @@
       </c>
       <c r="I104" t="s">
         <v>11</v>
+      </c>
+      <c r="J104" t="s">
+        <v>18</v>
+      </c>
+      <c r="K104" t="s">
+        <v>19</v>
       </c>
       <c r="L104" s="4" t="s">
         <v>19</v>
@@ -33201,10 +33863,13 @@
         <v>0</v>
       </c>
       <c r="X104">
-        <v>97.1</v>
+        <v>91.11</v>
+      </c>
+      <c r="Y104">
+        <v>85.1</v>
       </c>
     </row>
-    <row r="105" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A105" s="11" t="s">
         <v>26</v>
       </c>
@@ -33231,6 +33896,12 @@
       </c>
       <c r="I105" t="s">
         <v>11</v>
+      </c>
+      <c r="J105" t="s">
+        <v>18</v>
+      </c>
+      <c r="K105" t="s">
+        <v>19</v>
       </c>
       <c r="L105" s="4" t="s">
         <v>19</v>
@@ -33266,10 +33937,13 @@
         <v>0</v>
       </c>
       <c r="X105">
-        <v>81.400000000000006</v>
+        <v>54.599999999999994</v>
+      </c>
+      <c r="Y105">
+        <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A106" s="11" t="s">
         <v>25</v>
       </c>
@@ -33296,6 +33970,12 @@
       </c>
       <c r="I106" t="s">
         <v>11</v>
+      </c>
+      <c r="J106" t="s">
+        <v>18</v>
+      </c>
+      <c r="K106" t="s">
+        <v>19</v>
       </c>
       <c r="L106" s="4" t="s">
         <v>19</v>
@@ -33331,10 +34011,13 @@
         <v>0</v>
       </c>
       <c r="X106">
-        <v>115.25</v>
+        <v>44.74</v>
+      </c>
+      <c r="Y106">
+        <v>109.25</v>
       </c>
     </row>
-    <row r="107" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A107" s="11" t="s">
         <v>26</v>
       </c>
@@ -33361,6 +34044,12 @@
       </c>
       <c r="I107" t="s">
         <v>11</v>
+      </c>
+      <c r="J107" t="s">
+        <v>18</v>
+      </c>
+      <c r="K107" t="s">
+        <v>19</v>
       </c>
       <c r="L107" s="4" t="s">
         <v>20</v>
@@ -33396,10 +34085,13 @@
         <v>6.5555555555555545</v>
       </c>
       <c r="X107">
-        <v>51.65</v>
+        <v>103.7</v>
+      </c>
+      <c r="Y107">
+        <v>48.65</v>
       </c>
     </row>
-    <row r="108" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A108" s="11" t="s">
         <v>24</v>
       </c>
@@ -33426,6 +34118,12 @@
       </c>
       <c r="I108" t="s">
         <v>11</v>
+      </c>
+      <c r="J108" t="s">
+        <v>18</v>
+      </c>
+      <c r="K108" t="s">
+        <v>19</v>
       </c>
       <c r="L108" s="4" t="s">
         <v>20</v>
@@ -33461,10 +34159,13 @@
         <v>0.41244957396662674</v>
       </c>
       <c r="X108">
-        <v>72.599999999999994</v>
+        <v>67.28</v>
+      </c>
+      <c r="Y108">
+        <v>63.599999999999994</v>
       </c>
     </row>
-    <row r="109" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A109" s="11" t="s">
         <v>25</v>
       </c>
@@ -33491,6 +34192,12 @@
       </c>
       <c r="I109" t="s">
         <v>11</v>
+      </c>
+      <c r="J109" t="s">
+        <v>18</v>
+      </c>
+      <c r="K109" t="s">
+        <v>19</v>
       </c>
       <c r="L109" s="4" t="s">
         <v>20</v>
@@ -33525,11 +34232,14 @@
         <f t="shared" si="3"/>
         <v>0.75322187391152917</v>
       </c>
-      <c r="X109">
-        <v>63</v>
+      <c r="X109" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y109">
+        <v>48</v>
       </c>
     </row>
-    <row r="110" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A110" s="11" t="s">
         <v>25</v>
       </c>
@@ -33556,6 +34266,12 @@
       </c>
       <c r="I110" t="s">
         <v>11</v>
+      </c>
+      <c r="J110" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110" t="s">
+        <v>19</v>
       </c>
       <c r="L110" s="4" t="s">
         <v>20</v>
@@ -33590,11 +34306,14 @@
         <f t="shared" si="3"/>
         <v>0.55134751773049639</v>
       </c>
-      <c r="X110">
-        <v>142.1</v>
+      <c r="X110" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y110">
+        <v>127.1</v>
       </c>
     </row>
-    <row r="111" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A111" s="11" t="s">
         <v>24</v>
       </c>
@@ -33621,6 +34340,12 @@
       </c>
       <c r="I111" t="s">
         <v>11</v>
+      </c>
+      <c r="J111" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111" t="s">
+        <v>19</v>
       </c>
       <c r="L111" s="4" t="s">
         <v>20</v>
@@ -33655,11 +34380,14 @@
         <f t="shared" si="3"/>
         <v>0.30258751902587516</v>
       </c>
-      <c r="X111">
-        <v>56.400000000000006</v>
+      <c r="X111" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y111">
+        <v>50.400000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
         <v>26</v>
       </c>
@@ -33686,6 +34414,12 @@
       </c>
       <c r="I112" t="s">
         <v>11</v>
+      </c>
+      <c r="J112" t="s">
+        <v>18</v>
+      </c>
+      <c r="K112" t="s">
+        <v>19</v>
       </c>
       <c r="L112" s="4" t="s">
         <v>20</v>
@@ -33720,11 +34454,14 @@
         <f t="shared" si="3"/>
         <v>3.5318518518518522</v>
       </c>
-      <c r="X112">
-        <v>62.099999999999994</v>
+      <c r="X112" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y112">
+        <v>50.099999999999994</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A113" s="11" t="s">
         <v>26</v>
       </c>
@@ -33751,6 +34488,12 @@
       </c>
       <c r="I113" t="s">
         <v>11</v>
+      </c>
+      <c r="J113" t="s">
+        <v>18</v>
+      </c>
+      <c r="K113" t="s">
+        <v>19</v>
       </c>
       <c r="L113" s="4" t="s">
         <v>18</v>
@@ -33785,11 +34528,14 @@
         <f t="shared" si="3"/>
         <v>2.8692209450830148</v>
       </c>
-      <c r="X113">
-        <v>44.9</v>
+      <c r="X113" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y113">
+        <v>38.9</v>
       </c>
     </row>
-    <row r="114" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A114" s="11" t="s">
         <v>25</v>
       </c>
@@ -33816,6 +34562,12 @@
       </c>
       <c r="I114" t="s">
         <v>11</v>
+      </c>
+      <c r="J114" t="s">
+        <v>18</v>
+      </c>
+      <c r="K114" t="s">
+        <v>19</v>
       </c>
       <c r="L114" s="4" t="s">
         <v>18</v>
@@ -33850,11 +34602,14 @@
         <f t="shared" si="3"/>
         <v>0.38604435156159284</v>
       </c>
-      <c r="X114">
-        <v>152.94999999999999</v>
+      <c r="X114" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y114">
+        <v>128.94999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A115" s="11" t="s">
         <v>24</v>
       </c>
@@ -33881,6 +34636,12 @@
       </c>
       <c r="I115" t="s">
         <v>11</v>
+      </c>
+      <c r="J115" t="s">
+        <v>18</v>
+      </c>
+      <c r="K115" t="s">
+        <v>19</v>
       </c>
       <c r="L115" s="4" t="s">
         <v>18</v>
@@ -33915,11 +34676,14 @@
         <f t="shared" si="3"/>
         <v>0.24529458936742299</v>
       </c>
-      <c r="X115">
-        <v>141</v>
+      <c r="X115" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y115">
+        <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A116" s="11" t="s">
         <v>26</v>
       </c>
@@ -33946,6 +34710,12 @@
       </c>
       <c r="I116" t="s">
         <v>11</v>
+      </c>
+      <c r="J116" t="s">
+        <v>18</v>
+      </c>
+      <c r="K116" t="s">
+        <v>19</v>
       </c>
       <c r="L116" s="4" t="s">
         <v>19</v>
@@ -33981,10 +34751,13 @@
         <v>0</v>
       </c>
       <c r="X116">
-        <v>147</v>
+        <v>60.53</v>
+      </c>
+      <c r="Y116">
+        <v>105</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A117" s="11" t="s">
         <v>25</v>
       </c>
@@ -34011,6 +34784,12 @@
       </c>
       <c r="I117" t="s">
         <v>11</v>
+      </c>
+      <c r="J117" t="s">
+        <v>18</v>
+      </c>
+      <c r="K117" t="s">
+        <v>19</v>
       </c>
       <c r="L117" s="4" t="s">
         <v>19</v>
@@ -34046,10 +34825,13 @@
         <v>0</v>
       </c>
       <c r="X117">
-        <v>148.6</v>
+        <v>61.504999999999995</v>
+      </c>
+      <c r="Y117">
+        <v>100.6</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A118" s="11" t="s">
         <v>24</v>
       </c>
@@ -34076,6 +34858,12 @@
       </c>
       <c r="I118" t="s">
         <v>11</v>
+      </c>
+      <c r="J118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118" t="s">
+        <v>19</v>
       </c>
       <c r="L118" s="4" t="s">
         <v>19</v>
@@ -34111,10 +34899,13 @@
         <v>0</v>
       </c>
       <c r="X118">
-        <v>140.30000000000001</v>
+        <v>52.884999999999998</v>
+      </c>
+      <c r="Y118">
+        <v>104.3</v>
       </c>
     </row>
-    <row r="119" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A119" s="11" t="s">
         <v>24</v>
       </c>
@@ -34141,6 +34932,12 @@
       </c>
       <c r="I119" t="s">
         <v>11</v>
+      </c>
+      <c r="J119" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119" t="s">
+        <v>19</v>
       </c>
       <c r="L119" s="4" t="s">
         <v>17</v>
@@ -34176,10 +34973,13 @@
         <v>0.33533659241124175</v>
       </c>
       <c r="X119" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="120" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A120" s="11" t="s">
         <v>25</v>
       </c>
@@ -34206,6 +35006,12 @@
       </c>
       <c r="I120" t="s">
         <v>11</v>
+      </c>
+      <c r="J120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120" t="s">
+        <v>19</v>
       </c>
       <c r="L120" s="4" t="s">
         <v>17</v>
@@ -34241,10 +35047,13 @@
         <v>0.39418413353846099</v>
       </c>
       <c r="X120" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="121" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A121" s="11" t="s">
         <v>26</v>
       </c>
@@ -34271,6 +35080,12 @@
       </c>
       <c r="I121" t="s">
         <v>11</v>
+      </c>
+      <c r="J121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121" t="s">
+        <v>19</v>
       </c>
       <c r="L121" s="4" t="s">
         <v>17</v>
@@ -34306,10 +35121,13 @@
         <v>0.45289496269888418</v>
       </c>
       <c r="X121" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="122" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A122" s="11" t="s">
         <v>24</v>
       </c>
@@ -34336,6 +35154,12 @@
       </c>
       <c r="I122" t="s">
         <v>11</v>
+      </c>
+      <c r="J122" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122" t="s">
+        <v>19</v>
       </c>
       <c r="L122" s="4" t="s">
         <v>19</v>
@@ -34371,10 +35195,13 @@
         <v>0</v>
       </c>
       <c r="X122">
-        <v>164.05</v>
+        <v>74.27</v>
+      </c>
+      <c r="Y122">
+        <v>149.05000000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A123" s="11" t="s">
         <v>26</v>
       </c>
@@ -34401,6 +35228,12 @@
       </c>
       <c r="I123" t="s">
         <v>11</v>
+      </c>
+      <c r="J123" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123" t="s">
+        <v>19</v>
       </c>
       <c r="L123" s="4" t="s">
         <v>19</v>
@@ -34436,10 +35269,13 @@
         <v>0</v>
       </c>
       <c r="X123">
-        <v>146.69999999999999</v>
+        <v>48.55</v>
+      </c>
+      <c r="Y123">
+        <v>125.7</v>
       </c>
     </row>
-    <row r="124" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A124" s="11" t="s">
         <v>25</v>
       </c>
@@ -34466,6 +35302,12 @@
       </c>
       <c r="I124" t="s">
         <v>11</v>
+      </c>
+      <c r="J124" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124" t="s">
+        <v>19</v>
       </c>
       <c r="L124" s="4" t="s">
         <v>19</v>
@@ -34501,10 +35343,13 @@
         <v>0</v>
       </c>
       <c r="X124">
-        <v>161.85</v>
+        <v>60.539999999999992</v>
+      </c>
+      <c r="Y124">
+        <v>134.85</v>
       </c>
     </row>
-    <row r="125" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A125" s="11" t="s">
         <v>25</v>
       </c>
@@ -34531,6 +35376,12 @@
       </c>
       <c r="I125" t="s">
         <v>11</v>
+      </c>
+      <c r="J125" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125" t="s">
+        <v>19</v>
       </c>
       <c r="L125" s="4" t="s">
         <v>20</v>
@@ -34565,11 +35416,14 @@
         <f t="shared" si="3"/>
         <v>0.8192856338752994</v>
       </c>
-      <c r="X125">
-        <v>143.5</v>
+      <c r="X125" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y125">
+        <v>125.5</v>
       </c>
     </row>
-    <row r="126" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A126" s="11" t="s">
         <v>24</v>
       </c>
@@ -34596,6 +35450,12 @@
       </c>
       <c r="I126" t="s">
         <v>11</v>
+      </c>
+      <c r="J126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126" t="s">
+        <v>19</v>
       </c>
       <c r="L126" s="4" t="s">
         <v>20</v>
@@ -34630,11 +35490,14 @@
         <f t="shared" si="3"/>
         <v>0.32951262696859551</v>
       </c>
-      <c r="X126">
-        <v>88.25</v>
+      <c r="X126" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y126">
+        <v>70.25</v>
       </c>
     </row>
-    <row r="127" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A127" s="11" t="s">
         <v>26</v>
       </c>
@@ -34661,6 +35524,12 @@
       </c>
       <c r="I127" t="s">
         <v>11</v>
+      </c>
+      <c r="J127" t="s">
+        <v>18</v>
+      </c>
+      <c r="K127" t="s">
+        <v>19</v>
       </c>
       <c r="L127" s="4" t="s">
         <v>20</v>
@@ -34695,11 +35564,14 @@
         <f t="shared" si="3"/>
         <v>4.6381859410430835</v>
       </c>
-      <c r="X127">
-        <v>89.15</v>
+      <c r="X127" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y127">
+        <v>71.150000000000006</v>
       </c>
     </row>
-    <row r="128" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A128" s="11" t="s">
         <v>26</v>
       </c>
@@ -34726,6 +35598,12 @@
       </c>
       <c r="I128" t="s">
         <v>11</v>
+      </c>
+      <c r="J128" t="s">
+        <v>18</v>
+      </c>
+      <c r="K128" t="s">
+        <v>19</v>
       </c>
       <c r="L128" s="4" t="s">
         <v>18</v>
@@ -34760,11 +35638,14 @@
         <f t="shared" si="3"/>
         <v>3.9049808429118782</v>
       </c>
-      <c r="X128">
-        <v>32.85</v>
+      <c r="X128" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y128">
+        <v>26.85</v>
       </c>
     </row>
-    <row r="129" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A129" s="11" t="s">
         <v>24</v>
       </c>
@@ -34791,6 +35672,12 @@
       </c>
       <c r="I129" t="s">
         <v>11</v>
+      </c>
+      <c r="J129" t="s">
+        <v>18</v>
+      </c>
+      <c r="K129" t="s">
+        <v>19</v>
       </c>
       <c r="L129" s="4" t="s">
         <v>18</v>
@@ -34825,11 +35712,14 @@
         <f t="shared" si="3"/>
         <v>0.45861702071900667</v>
       </c>
-      <c r="X129">
-        <v>84.1</v>
+      <c r="X129" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y129">
+        <v>75.099999999999994</v>
       </c>
     </row>
-    <row r="130" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A130" s="11" t="s">
         <v>25</v>
       </c>
@@ -34856,6 +35746,12 @@
       </c>
       <c r="I130" t="s">
         <v>11</v>
+      </c>
+      <c r="J130" t="s">
+        <v>18</v>
+      </c>
+      <c r="K130" t="s">
+        <v>19</v>
       </c>
       <c r="L130" s="4" t="s">
         <v>18</v>
@@ -34890,11 +35786,14 @@
         <f t="shared" si="3"/>
         <v>0.89012732690893581</v>
       </c>
-      <c r="X130">
-        <v>41.85</v>
+      <c r="X130" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y130">
+        <v>35.85</v>
       </c>
     </row>
-    <row r="131" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A131" s="11" t="s">
         <v>26</v>
       </c>
@@ -34921,6 +35820,12 @@
       </c>
       <c r="I131" t="s">
         <v>11</v>
+      </c>
+      <c r="J131" t="s">
+        <v>18</v>
+      </c>
+      <c r="K131" t="s">
+        <v>19</v>
       </c>
       <c r="L131" s="4" t="s">
         <v>18</v>
@@ -34956,10 +35861,13 @@
         <v>6.5589317552444895</v>
       </c>
       <c r="X131">
-        <v>34.65</v>
+        <v>80.02000000000001</v>
+      </c>
+      <c r="Y131">
+        <v>28.65</v>
       </c>
     </row>
-    <row r="132" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A132" s="11" t="s">
         <v>25</v>
       </c>
@@ -34986,6 +35894,12 @@
       </c>
       <c r="I132" t="s">
         <v>11</v>
+      </c>
+      <c r="J132" t="s">
+        <v>18</v>
+      </c>
+      <c r="K132" t="s">
+        <v>19</v>
       </c>
       <c r="L132" s="4" t="s">
         <v>18</v>
@@ -35021,10 +35935,13 @@
         <v>0.8695633292575744</v>
       </c>
       <c r="X132">
-        <v>77.150000000000006</v>
+        <v>64.215000000000003</v>
+      </c>
+      <c r="Y132">
+        <v>68.150000000000006</v>
       </c>
     </row>
-    <row r="133" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A133" s="11" t="s">
         <v>24</v>
       </c>
@@ -35051,6 +35968,12 @@
       </c>
       <c r="I133" t="s">
         <v>11</v>
+      </c>
+      <c r="J133" t="s">
+        <v>18</v>
+      </c>
+      <c r="K133" t="s">
+        <v>19</v>
       </c>
       <c r="L133" s="4" t="s">
         <v>18</v>
@@ -35086,10 +36009,13 @@
         <v>0.55833216700603039</v>
       </c>
       <c r="X133">
-        <v>69.650000000000006</v>
+        <v>116.25999999999999</v>
+      </c>
+      <c r="Y133">
+        <v>57.65</v>
       </c>
     </row>
-    <row r="134" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A134" s="11" t="s">
         <v>24</v>
       </c>
@@ -35116,6 +36042,12 @@
       </c>
       <c r="I134" t="s">
         <v>11</v>
+      </c>
+      <c r="J134" t="s">
+        <v>18</v>
+      </c>
+      <c r="K134" t="s">
+        <v>19</v>
       </c>
       <c r="L134" s="4" t="s">
         <v>17</v>
@@ -35150,11 +36082,14 @@
         <f t="shared" si="5"/>
         <v>0.78786487949332296</v>
       </c>
-      <c r="X134">
-        <v>79.349999999999994</v>
+      <c r="X134" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y134">
+        <v>67.349999999999994</v>
       </c>
     </row>
-    <row r="135" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A135" s="11" t="s">
         <v>25</v>
       </c>
@@ -35181,6 +36116,12 @@
       </c>
       <c r="I135" t="s">
         <v>11</v>
+      </c>
+      <c r="J135" t="s">
+        <v>18</v>
+      </c>
+      <c r="K135" t="s">
+        <v>19</v>
       </c>
       <c r="L135" s="4" t="s">
         <v>17</v>
@@ -35215,11 +36156,14 @@
         <f t="shared" si="5"/>
         <v>1.1039122991984944</v>
       </c>
-      <c r="X135">
-        <v>47.7</v>
+      <c r="X135" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y135">
+        <v>41.7</v>
       </c>
     </row>
-    <row r="136" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A136" s="11" t="s">
         <v>26</v>
       </c>
@@ -35246,6 +36190,12 @@
       </c>
       <c r="I136" t="s">
         <v>11</v>
+      </c>
+      <c r="J136" t="s">
+        <v>18</v>
+      </c>
+      <c r="K136" t="s">
+        <v>19</v>
       </c>
       <c r="L136" s="4" t="s">
         <v>17</v>
@@ -35280,11 +36230,14 @@
         <f t="shared" si="5"/>
         <v>5.8663761801016694</v>
       </c>
-      <c r="X136">
-        <v>53.7</v>
+      <c r="X136" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y136">
+        <v>47.7</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A137" s="11" t="s">
         <v>25</v>
       </c>
@@ -35311,6 +36264,12 @@
       </c>
       <c r="I137" t="s">
         <v>11</v>
+      </c>
+      <c r="J137" t="s">
+        <v>18</v>
+      </c>
+      <c r="K137" t="s">
+        <v>19</v>
       </c>
       <c r="L137" s="4" t="s">
         <v>17</v>
@@ -35345,11 +36304,14 @@
         <f t="shared" si="5"/>
         <v>0.68768058838980817</v>
       </c>
-      <c r="X137">
-        <v>95.65</v>
+      <c r="X137" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y137">
+        <v>83.65</v>
       </c>
     </row>
-    <row r="138" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A138" s="11" t="s">
         <v>26</v>
       </c>
@@ -35376,6 +36338,12 @@
       </c>
       <c r="I138" t="s">
         <v>11</v>
+      </c>
+      <c r="J138" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138" t="s">
+        <v>19</v>
       </c>
       <c r="L138" s="4" t="s">
         <v>17</v>
@@ -35410,11 +36378,14 @@
         <f t="shared" si="5"/>
         <v>5.6691358024691345</v>
       </c>
-      <c r="X138">
-        <v>74.8</v>
+      <c r="X138" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y138">
+        <v>59.8</v>
       </c>
     </row>
-    <row r="139" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A139" s="11" t="s">
         <v>24</v>
       </c>
@@ -35441,6 +36412,12 @@
       </c>
       <c r="I139" t="s">
         <v>11</v>
+      </c>
+      <c r="J139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139" t="s">
+        <v>19</v>
       </c>
       <c r="L139" s="4" t="s">
         <v>17</v>
@@ -35476,10 +36453,13 @@
         <v>0.29425360538262318</v>
       </c>
       <c r="X139">
-        <v>159.35</v>
+        <v>74.319999999999993</v>
+      </c>
+      <c r="Y139">
+        <v>150.35</v>
       </c>
     </row>
-    <row r="140" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A140" s="11" t="s">
         <v>24</v>
       </c>
@@ -35506,6 +36486,12 @@
       </c>
       <c r="I140" t="s">
         <v>11</v>
+      </c>
+      <c r="J140" t="s">
+        <v>18</v>
+      </c>
+      <c r="K140" t="s">
+        <v>19</v>
       </c>
       <c r="L140" s="4" t="s">
         <v>19</v>
@@ -35540,11 +36526,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X140">
-        <v>126.85</v>
+      <c r="X140" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y140">
+        <v>108.85</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A141" s="11" t="s">
         <v>26</v>
       </c>
@@ -35571,6 +36560,12 @@
       </c>
       <c r="I141" t="s">
         <v>11</v>
+      </c>
+      <c r="J141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141" t="s">
+        <v>19</v>
       </c>
       <c r="L141" s="4" t="s">
         <v>19</v>
@@ -35605,11 +36600,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X141">
-        <v>123.2</v>
+      <c r="X141" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y141">
+        <v>102.2</v>
       </c>
     </row>
-    <row r="142" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A142" s="11" t="s">
         <v>25</v>
       </c>
@@ -35636,6 +36634,12 @@
       </c>
       <c r="I142" t="s">
         <v>11</v>
+      </c>
+      <c r="J142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142" t="s">
+        <v>19</v>
       </c>
       <c r="L142" s="4" t="s">
         <v>19</v>
@@ -35670,11 +36674,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X142">
-        <v>154.80000000000001</v>
+      <c r="X142" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y142">
+        <v>136.80000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A143" s="11" t="s">
         <v>25</v>
       </c>
@@ -35701,6 +36708,12 @@
       </c>
       <c r="I143" t="s">
         <v>11</v>
+      </c>
+      <c r="J143" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143" t="s">
+        <v>19</v>
       </c>
       <c r="L143" s="4" t="s">
         <v>18</v>
@@ -35735,11 +36748,14 @@
         <f t="shared" si="5"/>
         <v>1.0766708479126779</v>
       </c>
-      <c r="X143">
-        <v>95.5</v>
+      <c r="X143" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y143">
+        <v>89.5</v>
       </c>
     </row>
-    <row r="144" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A144" s="11" t="s">
         <v>26</v>
       </c>
@@ -35766,6 +36782,12 @@
       </c>
       <c r="I144" t="s">
         <v>11</v>
+      </c>
+      <c r="J144" t="s">
+        <v>18</v>
+      </c>
+      <c r="K144" t="s">
+        <v>19</v>
       </c>
       <c r="L144" s="4" t="s">
         <v>18</v>
@@ -35800,11 +36822,14 @@
         <f t="shared" si="5"/>
         <v>5.9680464778503994</v>
       </c>
-      <c r="X144">
-        <v>52.75</v>
+      <c r="X144" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y144">
+        <v>34.75</v>
       </c>
     </row>
-    <row r="145" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A145" s="11" t="s">
         <v>24</v>
       </c>
@@ -35831,6 +36856,12 @@
       </c>
       <c r="I145" t="s">
         <v>11</v>
+      </c>
+      <c r="J145" t="s">
+        <v>18</v>
+      </c>
+      <c r="K145" t="s">
+        <v>19</v>
       </c>
       <c r="L145" s="4" t="s">
         <v>18</v>
@@ -35865,11 +36896,14 @@
         <f t="shared" si="5"/>
         <v>0.69805644763398045</v>
       </c>
-      <c r="X145">
-        <v>90.65</v>
+      <c r="X145" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y145">
+        <v>78.650000000000006</v>
       </c>
     </row>
-    <row r="146" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A146" s="11" t="s">
         <v>26</v>
       </c>
@@ -35896,6 +36930,12 @@
       </c>
       <c r="I146" t="s">
         <v>11</v>
+      </c>
+      <c r="J146" t="s">
+        <v>18</v>
+      </c>
+      <c r="K146" t="s">
+        <v>19</v>
       </c>
       <c r="L146" s="4" t="s">
         <v>20</v>
@@ -35931,10 +36971,13 @@
         <v>4.5164750957854398</v>
       </c>
       <c r="X146">
-        <v>56.65</v>
+        <v>57.89</v>
+      </c>
+      <c r="Y146">
+        <v>47.65</v>
       </c>
     </row>
-    <row r="147" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A147" s="11" t="s">
         <v>24</v>
       </c>
@@ -35961,6 +37004,12 @@
       </c>
       <c r="I147" t="s">
         <v>11</v>
+      </c>
+      <c r="J147" t="s">
+        <v>18</v>
+      </c>
+      <c r="K147" t="s">
+        <v>19</v>
       </c>
       <c r="L147" s="4" t="s">
         <v>20</v>
@@ -35996,10 +37045,13 @@
         <v>0.44988145841959709</v>
       </c>
       <c r="X147">
-        <v>66.5</v>
+        <v>62.320000000000007</v>
+      </c>
+      <c r="Y147">
+        <v>54.5</v>
       </c>
     </row>
-    <row r="148" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A148" s="11" t="s">
         <v>25</v>
       </c>
@@ -36026,6 +37078,12 @@
       </c>
       <c r="I148" t="s">
         <v>11</v>
+      </c>
+      <c r="J148" t="s">
+        <v>18</v>
+      </c>
+      <c r="K148" t="s">
+        <v>19</v>
       </c>
       <c r="L148" s="4" t="s">
         <v>20</v>
@@ -36061,10 +37119,13 @@
         <v>0.59836874492046921</v>
       </c>
       <c r="X148">
-        <v>66.8</v>
+        <v>55.36</v>
+      </c>
+      <c r="Y148">
+        <v>51.8</v>
       </c>
     </row>
-    <row r="149" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A149" s="11" t="s">
         <v>25</v>
       </c>
@@ -36091,6 +37152,12 @@
       </c>
       <c r="I149" t="s">
         <v>11</v>
+      </c>
+      <c r="J149" t="s">
+        <v>18</v>
+      </c>
+      <c r="K149" t="s">
+        <v>19</v>
       </c>
       <c r="L149" s="4" t="s">
         <v>17</v>
@@ -36126,10 +37193,13 @@
         <v>0.58361879030572017</v>
       </c>
       <c r="X149" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="150" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A150" s="11" t="s">
         <v>24</v>
       </c>
@@ -36156,6 +37226,12 @@
       </c>
       <c r="I150" t="s">
         <v>11</v>
+      </c>
+      <c r="J150" t="s">
+        <v>18</v>
+      </c>
+      <c r="K150" t="s">
+        <v>19</v>
       </c>
       <c r="L150" s="4" t="s">
         <v>17</v>
@@ -36191,10 +37267,13 @@
         <v>0.20136882759191949</v>
       </c>
       <c r="X150" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="Y150" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="151" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A151" s="11" t="s">
         <v>26</v>
       </c>
@@ -36221,6 +37300,12 @@
       </c>
       <c r="I151" t="s">
         <v>11</v>
+      </c>
+      <c r="J151" t="s">
+        <v>18</v>
+      </c>
+      <c r="K151" t="s">
+        <v>19</v>
       </c>
       <c r="L151" s="4" t="s">
         <v>17</v>
@@ -36256,10 +37341,13 @@
         <v>1.8469538926681786</v>
       </c>
       <c r="X151" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="Y151" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="152" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A152" s="11" t="s">
         <v>26</v>
       </c>
@@ -36286,6 +37374,12 @@
       </c>
       <c r="I152" t="s">
         <v>11</v>
+      </c>
+      <c r="J152" t="s">
+        <v>18</v>
+      </c>
+      <c r="K152" t="s">
+        <v>19</v>
       </c>
       <c r="L152" s="4" t="s">
         <v>19</v>
@@ -36321,10 +37415,13 @@
         <v>0</v>
       </c>
       <c r="X152">
-        <v>72.449999999999989</v>
+        <v>39.594999999999999</v>
+      </c>
+      <c r="Y152">
+        <v>60.449999999999996</v>
       </c>
     </row>
-    <row r="153" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A153" s="11" t="s">
         <v>25</v>
       </c>
@@ -36351,6 +37448,12 @@
       </c>
       <c r="I153" t="s">
         <v>11</v>
+      </c>
+      <c r="J153" t="s">
+        <v>18</v>
+      </c>
+      <c r="K153" t="s">
+        <v>19</v>
       </c>
       <c r="L153" s="4" t="s">
         <v>19</v>
@@ -36386,10 +37489,13 @@
         <v>0</v>
       </c>
       <c r="X153">
-        <v>116.7</v>
+        <v>55.660000000000004</v>
+      </c>
+      <c r="Y153">
+        <v>107.7</v>
       </c>
     </row>
-    <row r="154" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A154" s="11" t="s">
         <v>24</v>
       </c>
@@ -36416,6 +37522,12 @@
       </c>
       <c r="I154" t="s">
         <v>11</v>
+      </c>
+      <c r="J154" t="s">
+        <v>18</v>
+      </c>
+      <c r="K154" t="s">
+        <v>19</v>
       </c>
       <c r="L154" s="4" t="s">
         <v>19</v>
@@ -36451,10 +37563,13 @@
         <v>0</v>
       </c>
       <c r="X154">
-        <v>77.75</v>
+        <v>68.160000000000011</v>
+      </c>
+      <c r="Y154">
+        <v>71.75</v>
       </c>
     </row>
-    <row r="155" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A155" s="11" t="s">
         <v>25</v>
       </c>
@@ -36481,6 +37596,12 @@
       </c>
       <c r="I155" t="s">
         <v>11</v>
+      </c>
+      <c r="J155" t="s">
+        <v>18</v>
+      </c>
+      <c r="K155" t="s">
+        <v>19</v>
       </c>
       <c r="L155" s="4" t="s">
         <v>17</v>
@@ -36516,10 +37637,13 @@
         <v>0.20075650118203311</v>
       </c>
       <c r="X155">
-        <v>117.7</v>
+        <v>73.209999999999994</v>
+      </c>
+      <c r="Y155">
+        <v>96.7</v>
       </c>
     </row>
-    <row r="156" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A156" s="11" t="s">
         <v>24</v>
       </c>
@@ -36546,6 +37670,12 @@
       </c>
       <c r="I156" t="s">
         <v>11</v>
+      </c>
+      <c r="J156" t="s">
+        <v>18</v>
+      </c>
+      <c r="K156" t="s">
+        <v>19</v>
       </c>
       <c r="L156" s="4" t="s">
         <v>17</v>
@@ -36581,10 +37711,13 @@
         <v>0.15763233553187891</v>
       </c>
       <c r="X156">
-        <v>146.85</v>
+        <v>60.019999999999996</v>
+      </c>
+      <c r="Y156">
+        <v>137.85</v>
       </c>
     </row>
-    <row r="157" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A157" s="11" t="s">
         <v>26</v>
       </c>
@@ -36611,6 +37744,12 @@
       </c>
       <c r="I157" t="s">
         <v>11</v>
+      </c>
+      <c r="J157" t="s">
+        <v>18</v>
+      </c>
+      <c r="K157" t="s">
+        <v>19</v>
       </c>
       <c r="L157" s="4" t="s">
         <v>17</v>
@@ -36646,10 +37785,13 @@
         <v>3.5610074074074078</v>
       </c>
       <c r="X157">
-        <v>84.3</v>
+        <v>51.97</v>
+      </c>
+      <c r="Y157">
+        <v>75.3</v>
       </c>
     </row>
-    <row r="158" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A158" s="11" t="s">
         <v>24</v>
       </c>
@@ -36676,6 +37818,12 @@
       </c>
       <c r="I158" t="s">
         <v>11</v>
+      </c>
+      <c r="J158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158" t="s">
+        <v>19</v>
       </c>
       <c r="L158" s="4" t="s">
         <v>17</v>
@@ -36711,10 +37859,13 @@
         <v>0.27151023169288013</v>
       </c>
       <c r="X158">
-        <v>80.650000000000006</v>
+        <v>45.96</v>
+      </c>
+      <c r="Y158">
+        <v>65.650000000000006</v>
       </c>
     </row>
-    <row r="159" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A159" s="11" t="s">
         <v>26</v>
       </c>
@@ -36741,6 +37892,12 @@
       </c>
       <c r="I159" t="s">
         <v>11</v>
+      </c>
+      <c r="J159" t="s">
+        <v>18</v>
+      </c>
+      <c r="K159" t="s">
+        <v>19</v>
       </c>
       <c r="L159" s="4" t="s">
         <v>17</v>
@@ -36776,10 +37933,13 @@
         <v>4.6459259259259262</v>
       </c>
       <c r="X159">
-        <v>64.3</v>
+        <v>40.18</v>
+      </c>
+      <c r="Y159">
+        <v>52.3</v>
       </c>
     </row>
-    <row r="160" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A160" s="11" t="s">
         <v>25</v>
       </c>
@@ -36806,6 +37966,12 @@
       </c>
       <c r="I160" t="s">
         <v>11</v>
+      </c>
+      <c r="J160" t="s">
+        <v>18</v>
+      </c>
+      <c r="K160" t="s">
+        <v>19</v>
       </c>
       <c r="L160" s="4" t="s">
         <v>17</v>
@@ -36841,10 +38007,13 @@
         <v>0.53692671394799041</v>
       </c>
       <c r="X160">
-        <v>69.099999999999994</v>
+        <v>35.770000000000003</v>
+      </c>
+      <c r="Y160">
+        <v>57.1</v>
       </c>
     </row>
-    <row r="161" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A161" s="11" t="s">
         <v>26</v>
       </c>
@@ -36871,6 +38040,12 @@
       </c>
       <c r="I161" t="s">
         <v>11</v>
+      </c>
+      <c r="J161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K161" t="s">
+        <v>19</v>
       </c>
       <c r="L161" s="4" t="s">
         <v>20</v>
@@ -36906,10 +38081,13 @@
         <v>4.5475095785440605</v>
       </c>
       <c r="X161">
-        <v>45.25</v>
+        <v>33.69</v>
+      </c>
+      <c r="Y161">
+        <v>33.25</v>
       </c>
     </row>
-    <row r="162" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A162" s="11" t="s">
         <v>24</v>
       </c>
@@ -36936,6 +38114,12 @@
       </c>
       <c r="I162" t="s">
         <v>11</v>
+      </c>
+      <c r="J162" t="s">
+        <v>18</v>
+      </c>
+      <c r="K162" t="s">
+        <v>19</v>
       </c>
       <c r="L162" s="4" t="s">
         <v>20</v>
@@ -36971,10 +38155,13 @@
         <v>0.5568396832135688</v>
       </c>
       <c r="X162">
-        <v>96.75</v>
+        <v>51.42</v>
+      </c>
+      <c r="Y162">
+        <v>87.75</v>
       </c>
     </row>
-    <row r="163" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A163" s="11" t="s">
         <v>25</v>
       </c>
@@ -37001,6 +38188,12 @@
       </c>
       <c r="I163" t="s">
         <v>11</v>
+      </c>
+      <c r="J163" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163" t="s">
+        <v>19</v>
       </c>
       <c r="L163" s="4" t="s">
         <v>20</v>
@@ -37036,10 +38229,13 @@
         <v>0.94929176825728578</v>
       </c>
       <c r="X163">
-        <v>68.05</v>
+        <v>80.199999999999989</v>
+      </c>
+      <c r="Y163">
+        <v>62.05</v>
       </c>
     </row>
-    <row r="164" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A164" s="11" t="s">
         <v>24</v>
       </c>
@@ -37066,6 +38262,12 @@
       </c>
       <c r="I164" t="s">
         <v>11</v>
+      </c>
+      <c r="J164" t="s">
+        <v>18</v>
+      </c>
+      <c r="K164" t="s">
+        <v>19</v>
       </c>
       <c r="L164" s="4" t="s">
         <v>18</v>
@@ -37100,11 +38302,14 @@
         <f t="shared" si="5"/>
         <v>0.77352298590999291</v>
       </c>
-      <c r="X164">
-        <v>82.75</v>
+      <c r="X164" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y164">
+        <v>67.75</v>
       </c>
     </row>
-    <row r="165" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A165" s="11" t="s">
         <v>25</v>
       </c>
@@ -37131,6 +38336,12 @@
       </c>
       <c r="I165" t="s">
         <v>11</v>
+      </c>
+      <c r="J165" t="s">
+        <v>18</v>
+      </c>
+      <c r="K165" t="s">
+        <v>19</v>
       </c>
       <c r="L165" s="4" t="s">
         <v>18</v>
@@ -37165,11 +38376,14 @@
         <f t="shared" si="5"/>
         <v>1.0429774739539053</v>
       </c>
-      <c r="X165">
-        <v>71.5</v>
+      <c r="X165" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y165">
+        <v>62.5</v>
       </c>
     </row>
-    <row r="166" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A166" s="11" t="s">
         <v>26</v>
       </c>
@@ -37196,6 +38410,12 @@
       </c>
       <c r="I166" t="s">
         <v>11</v>
+      </c>
+      <c r="J166" t="s">
+        <v>18</v>
+      </c>
+      <c r="K166" t="s">
+        <v>19</v>
       </c>
       <c r="L166" s="4" t="s">
         <v>18</v>
@@ -37230,11 +38450,14 @@
         <f t="shared" si="5"/>
         <v>6.2079619726678548</v>
       </c>
-      <c r="X166">
-        <v>62.1</v>
+      <c r="X166" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y166">
+        <v>56.1</v>
       </c>
     </row>
-    <row r="167" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A167" s="11" t="s">
         <v>24</v>
       </c>
@@ -37261,6 +38484,12 @@
       </c>
       <c r="I167" t="s">
         <v>11</v>
+      </c>
+      <c r="J167" t="s">
+        <v>18</v>
+      </c>
+      <c r="K167" t="s">
+        <v>19</v>
       </c>
       <c r="L167" s="4" t="s">
         <v>18</v>
@@ -37296,10 +38525,13 @@
         <v>0.4393288991619102</v>
       </c>
       <c r="X167">
-        <v>78.7</v>
+        <v>104.03</v>
+      </c>
+      <c r="Y167">
+        <v>69.7</v>
       </c>
     </row>
-    <row r="168" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A168" s="11" t="s">
         <v>26</v>
       </c>
@@ -37326,6 +38558,12 @@
       </c>
       <c r="I168" t="s">
         <v>11</v>
+      </c>
+      <c r="J168" t="s">
+        <v>18</v>
+      </c>
+      <c r="K168" t="s">
+        <v>19</v>
       </c>
       <c r="L168" s="4" t="s">
         <v>18</v>
@@ -37361,10 +38599,13 @@
         <v>4.293742017879949</v>
       </c>
       <c r="X168">
-        <v>46.55</v>
+        <v>23.725000000000001</v>
+      </c>
+      <c r="Y168">
+        <v>40.549999999999997</v>
       </c>
     </row>
-    <row r="169" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A169" s="11" t="s">
         <v>25</v>
       </c>
@@ -37391,6 +38632,12 @@
       </c>
       <c r="I169" t="s">
         <v>11</v>
+      </c>
+      <c r="J169" t="s">
+        <v>18</v>
+      </c>
+      <c r="K169" t="s">
+        <v>19</v>
       </c>
       <c r="L169" s="4" t="s">
         <v>18</v>
@@ -37426,10 +38673,13 @@
         <v>0.74741669569255786</v>
       </c>
       <c r="X169">
-        <v>36.4</v>
+        <v>117.05</v>
+      </c>
+      <c r="Y169">
+        <v>27.4</v>
       </c>
     </row>
-    <row r="170" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A170" s="11" t="s">
         <v>26</v>
       </c>
@@ -37456,6 +38706,12 @@
       </c>
       <c r="I170" t="s">
         <v>11</v>
+      </c>
+      <c r="J170" t="s">
+        <v>18</v>
+      </c>
+      <c r="K170" t="s">
+        <v>19</v>
       </c>
       <c r="L170" s="4" t="s">
         <v>19</v>
@@ -37490,11 +38746,14 @@
         <f>V170/Q170</f>
         <v>0</v>
       </c>
-      <c r="X170">
-        <v>145.5</v>
+      <c r="X170" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y170">
+        <v>115.5</v>
       </c>
     </row>
-    <row r="171" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A171" s="11" t="s">
         <v>25</v>
       </c>
@@ -37521,6 +38780,12 @@
       </c>
       <c r="I171" t="s">
         <v>11</v>
+      </c>
+      <c r="J171" t="s">
+        <v>18</v>
+      </c>
+      <c r="K171" t="s">
+        <v>19</v>
       </c>
       <c r="L171" s="4" t="s">
         <v>19</v>
@@ -37555,11 +38820,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X171">
-        <v>173.4</v>
+      <c r="X171" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y171">
+        <v>146.4</v>
       </c>
     </row>
-    <row r="172" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A172" s="11" t="s">
         <v>24</v>
       </c>
@@ -37586,6 +38854,12 @@
       </c>
       <c r="I172" t="s">
         <v>11</v>
+      </c>
+      <c r="J172" t="s">
+        <v>18</v>
+      </c>
+      <c r="K172" t="s">
+        <v>19</v>
       </c>
       <c r="L172" s="4" t="s">
         <v>19</v>
@@ -37620,11 +38894,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X172">
-        <v>75</v>
+      <c r="X172" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y172">
+        <v>66</v>
       </c>
     </row>
-    <row r="173" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A173" s="11" t="s">
         <v>25</v>
       </c>
@@ -37651,6 +38928,12 @@
       </c>
       <c r="I173" t="s">
         <v>11</v>
+      </c>
+      <c r="J173" t="s">
+        <v>18</v>
+      </c>
+      <c r="K173" t="s">
+        <v>19</v>
       </c>
       <c r="L173" s="4" t="s">
         <v>18</v>
@@ -37685,11 +38968,14 @@
         <f t="shared" si="5"/>
         <v>0.69271901647380585</v>
       </c>
-      <c r="X173">
-        <v>46.3</v>
+      <c r="X173" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y173">
+        <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="174" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A174" s="11" t="s">
         <v>24</v>
       </c>
@@ -37716,6 +39002,12 @@
       </c>
       <c r="I174" t="s">
         <v>11</v>
+      </c>
+      <c r="J174" t="s">
+        <v>18</v>
+      </c>
+      <c r="K174" t="s">
+        <v>19</v>
       </c>
       <c r="L174" s="4" t="s">
         <v>18</v>
@@ -37750,11 +39042,14 @@
         <f t="shared" si="5"/>
         <v>0.27171092976083783</v>
       </c>
-      <c r="X174">
-        <v>82.449999999999989</v>
+      <c r="X174" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y174">
+        <v>70.449999999999989</v>
       </c>
     </row>
-    <row r="175" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A175" s="11" t="s">
         <v>26</v>
       </c>
@@ -37781,6 +39076,12 @@
       </c>
       <c r="I175" t="s">
         <v>11</v>
+      </c>
+      <c r="J175" t="s">
+        <v>18</v>
+      </c>
+      <c r="K175" t="s">
+        <v>19</v>
       </c>
       <c r="L175" s="4" t="s">
         <v>18</v>
@@ -37815,11 +39116,14 @@
         <f t="shared" si="5"/>
         <v>4.6323116219667941</v>
       </c>
-      <c r="X175">
-        <v>36.65</v>
+      <c r="X175" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y175">
+        <v>27.65</v>
       </c>
     </row>
-    <row r="176" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A176" s="11" t="s">
         <v>24</v>
       </c>
@@ -37846,6 +39150,12 @@
       </c>
       <c r="I176" t="s">
         <v>11</v>
+      </c>
+      <c r="J176" t="s">
+        <v>18</v>
+      </c>
+      <c r="K176" t="s">
+        <v>19</v>
       </c>
       <c r="L176" s="4" t="s">
         <v>17</v>
@@ -37881,10 +39191,13 @@
         <v>0.61389265273281246</v>
       </c>
       <c r="X176">
-        <v>74.3</v>
+        <v>42.224999999999994</v>
+      </c>
+      <c r="Y176">
+        <v>65.3</v>
       </c>
     </row>
-    <row r="177" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A177" s="11" t="s">
         <v>25</v>
       </c>
@@ -37911,6 +39224,12 @@
       </c>
       <c r="I177" t="s">
         <v>11</v>
+      </c>
+      <c r="J177" t="s">
+        <v>18</v>
+      </c>
+      <c r="K177" t="s">
+        <v>19</v>
       </c>
       <c r="L177" s="4" t="s">
         <v>17</v>
@@ -37946,10 +39265,13 @@
         <v>0.76126018886961655</v>
       </c>
       <c r="X177">
-        <v>41.8</v>
+        <v>26.91</v>
+      </c>
+      <c r="Y177">
+        <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="178" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A178" s="11" t="s">
         <v>26</v>
       </c>
@@ -37976,6 +39298,12 @@
       </c>
       <c r="I178" t="s">
         <v>11</v>
+      </c>
+      <c r="J178" t="s">
+        <v>18</v>
+      </c>
+      <c r="K178" t="s">
+        <v>19</v>
       </c>
       <c r="L178" s="4" t="s">
         <v>17</v>
@@ -38011,10 +39339,13 @@
         <v>3.6533967122202413</v>
       </c>
       <c r="X178">
-        <v>63.8</v>
+        <v>24.055</v>
+      </c>
+      <c r="Y178">
+        <v>60.8</v>
       </c>
     </row>
-    <row r="179" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A179" s="11" t="s">
         <v>25</v>
       </c>
@@ -38041,6 +39372,12 @@
       </c>
       <c r="I179" t="s">
         <v>11</v>
+      </c>
+      <c r="J179" t="s">
+        <v>18</v>
+      </c>
+      <c r="K179" t="s">
+        <v>19</v>
       </c>
       <c r="L179" s="4" t="s">
         <v>20</v>
@@ -38076,10 +39413,13 @@
         <v>0.64003473729917493</v>
       </c>
       <c r="X179" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="Y179" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="180" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A180" s="11" t="s">
         <v>24</v>
       </c>
@@ -38106,6 +39446,12 @@
       </c>
       <c r="I180" t="s">
         <v>11</v>
+      </c>
+      <c r="J180" t="s">
+        <v>18</v>
+      </c>
+      <c r="K180" t="s">
+        <v>19</v>
       </c>
       <c r="L180" s="4" t="s">
         <v>20</v>
@@ -38141,10 +39487,13 @@
         <v>0.24905345192364103</v>
       </c>
       <c r="X180" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="Y180" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="181" spans="1:24" ht="16" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:25" ht="16" x14ac:dyDescent="0.35">
       <c r="A181" s="11" t="s">
         <v>26</v>
       </c>
@@ -38171,6 +39520,12 @@
       </c>
       <c r="I181" t="s">
         <v>11</v>
+      </c>
+      <c r="J181" t="s">
+        <v>18</v>
+      </c>
+      <c r="K181" t="s">
+        <v>19</v>
       </c>
       <c r="L181" s="4" t="s">
         <v>20</v>
@@ -38206,10 +39561,13 @@
         <v>2.5451247165532878</v>
       </c>
       <c r="X181" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="Y181" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="182" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>24</v>
       </c>
@@ -38237,6 +39595,9 @@
       <c r="I182" t="s">
         <v>15</v>
       </c>
+      <c r="J182" t="s">
+        <v>19</v>
+      </c>
       <c r="K182" t="s">
         <v>17</v>
       </c>
@@ -38273,11 +39634,11 @@
       <c r="W182">
         <v>0.71539088771033688</v>
       </c>
-      <c r="X182">
+      <c r="Y182">
         <v>58.85</v>
       </c>
     </row>
-    <row r="183" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>25</v>
       </c>
@@ -38305,6 +39666,9 @@
       <c r="I183" t="s">
         <v>15</v>
       </c>
+      <c r="J183" t="s">
+        <v>19</v>
+      </c>
       <c r="K183" t="s">
         <v>17</v>
       </c>
@@ -38341,11 +39705,11 @@
       <c r="W183">
         <v>0.93400289844255358</v>
       </c>
-      <c r="X183">
+      <c r="Y183">
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="184" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>26</v>
       </c>
@@ -38373,6 +39737,9 @@
       <c r="I184" t="s">
         <v>15</v>
       </c>
+      <c r="J184" t="s">
+        <v>19</v>
+      </c>
       <c r="K184" t="s">
         <v>17</v>
       </c>
@@ -38409,11 +39776,11 @@
       <c r="W184">
         <v>5.3522167487684724</v>
       </c>
-      <c r="X184">
+      <c r="Y184">
         <v>89.6</v>
       </c>
     </row>
-    <row r="185" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>26</v>
       </c>
@@ -38441,6 +39808,9 @@
       <c r="I185" t="s">
         <v>15</v>
       </c>
+      <c r="J185" t="s">
+        <v>19</v>
+      </c>
       <c r="K185" t="s">
         <v>18</v>
       </c>
@@ -38474,11 +39844,11 @@
       <c r="W185">
         <v>2.6689142857142856</v>
       </c>
-      <c r="X185">
+      <c r="Y185">
         <v>62.95</v>
       </c>
     </row>
-    <row r="186" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>25</v>
       </c>
@@ -38506,6 +39876,9 @@
       <c r="I186" t="s">
         <v>15</v>
       </c>
+      <c r="J186" t="s">
+        <v>19</v>
+      </c>
       <c r="K186" t="s">
         <v>18</v>
       </c>
@@ -38539,11 +39912,11 @@
       <c r="W186">
         <v>0.56872340425531909</v>
       </c>
-      <c r="X186">
+      <c r="Y186">
         <v>121.75</v>
       </c>
     </row>
-    <row r="187" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>24</v>
       </c>
@@ -38571,6 +39944,9 @@
       <c r="I187" t="s">
         <v>15</v>
       </c>
+      <c r="J187" t="s">
+        <v>19</v>
+      </c>
       <c r="K187" t="s">
         <v>18</v>
       </c>
@@ -38604,11 +39980,11 @@
       <c r="W187">
         <v>0.25153294194390086</v>
       </c>
-      <c r="X187">
+      <c r="Y187">
         <v>117.05</v>
       </c>
     </row>
-    <row r="188" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>26</v>
       </c>
@@ -38636,6 +40012,9 @@
       <c r="I188" t="s">
         <v>15</v>
       </c>
+      <c r="J188" t="s">
+        <v>19</v>
+      </c>
       <c r="K188" t="s">
         <v>17</v>
       </c>
@@ -38672,11 +40051,11 @@
       <c r="W188">
         <v>7.5407881773399028</v>
       </c>
-      <c r="X188">
+      <c r="Y188">
         <v>115.44999999999999</v>
       </c>
     </row>
-    <row r="189" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>24</v>
       </c>
@@ -38704,6 +40083,9 @@
       <c r="I189" t="s">
         <v>15</v>
       </c>
+      <c r="J189" t="s">
+        <v>19</v>
+      </c>
       <c r="K189" t="s">
         <v>17</v>
       </c>
@@ -38740,11 +40122,11 @@
       <c r="W189">
         <v>0.78571765514545844</v>
       </c>
-      <c r="X189">
+      <c r="Y189">
         <v>94.5</v>
       </c>
     </row>
-    <row r="190" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>25</v>
       </c>
@@ -38772,6 +40154,9 @@
       <c r="I190" t="s">
         <v>15</v>
       </c>
+      <c r="J190" t="s">
+        <v>19</v>
+      </c>
       <c r="K190" t="s">
         <v>17</v>
       </c>
@@ -38808,11 +40193,11 @@
       <c r="W190">
         <v>1.1349206349206347</v>
       </c>
-      <c r="X190">
+      <c r="Y190">
         <v>72.599999999999994</v>
       </c>
     </row>
-    <row r="191" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>25</v>
       </c>
@@ -38840,6 +40225,9 @@
       <c r="I191" t="s">
         <v>15</v>
       </c>
+      <c r="J191" t="s">
+        <v>19</v>
+      </c>
       <c r="K191" t="s">
         <v>18</v>
       </c>
@@ -38870,11 +40258,11 @@
       <c r="W191">
         <v>0</v>
       </c>
-      <c r="X191">
+      <c r="Y191">
         <v>84.1</v>
       </c>
     </row>
-    <row r="192" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>26</v>
       </c>
@@ -38902,6 +40290,9 @@
       <c r="I192" t="s">
         <v>15</v>
       </c>
+      <c r="J192" t="s">
+        <v>19</v>
+      </c>
       <c r="K192" t="s">
         <v>18</v>
       </c>
@@ -38932,11 +40323,11 @@
       <c r="W192">
         <v>0</v>
       </c>
-      <c r="X192">
+      <c r="Y192">
         <v>79.150000000000006</v>
       </c>
     </row>
-    <row r="193" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>24</v>
       </c>
@@ -38964,6 +40355,9 @@
       <c r="I193" t="s">
         <v>15</v>
       </c>
+      <c r="J193" t="s">
+        <v>19</v>
+      </c>
       <c r="K193" t="s">
         <v>18</v>
       </c>
@@ -38994,11 +40388,11 @@
       <c r="W193">
         <v>0</v>
       </c>
-      <c r="X193">
+      <c r="Y193">
         <v>161.15</v>
       </c>
     </row>
-    <row r="194" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>24</v>
       </c>
@@ -39026,6 +40420,9 @@
       <c r="I194" t="s">
         <v>15</v>
       </c>
+      <c r="J194" t="s">
+        <v>19</v>
+      </c>
       <c r="K194" t="s">
         <v>19</v>
       </c>
@@ -39059,11 +40456,11 @@
       <c r="W194">
         <v>0.17598097565104889</v>
       </c>
-      <c r="X194">
+      <c r="Y194">
         <v>93.3</v>
       </c>
     </row>
-    <row r="195" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>26</v>
       </c>
@@ -39091,6 +40488,9 @@
       <c r="I195" t="s">
         <v>15</v>
       </c>
+      <c r="J195" t="s">
+        <v>19</v>
+      </c>
       <c r="K195" t="s">
         <v>19</v>
       </c>
@@ -39124,11 +40524,11 @@
       <c r="W195">
         <v>0.9126050420168067</v>
       </c>
-      <c r="X195">
+      <c r="Y195">
         <v>48.7</v>
       </c>
     </row>
-    <row r="196" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>25</v>
       </c>
@@ -39156,6 +40556,9 @@
       <c r="I196" t="s">
         <v>15</v>
       </c>
+      <c r="J196" t="s">
+        <v>19</v>
+      </c>
       <c r="K196" t="s">
         <v>19</v>
       </c>
@@ -39189,11 +40592,11 @@
       <c r="W196">
         <v>0.31798761745285808</v>
       </c>
-      <c r="X196">
+      <c r="Y196">
         <v>43.15</v>
       </c>
     </row>
-    <row r="197" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>26</v>
       </c>
@@ -39221,6 +40624,9 @@
       <c r="I197" t="s">
         <v>15</v>
       </c>
+      <c r="J197" t="s">
+        <v>19</v>
+      </c>
       <c r="K197" t="s">
         <v>20</v>
       </c>
@@ -39257,11 +40663,11 @@
       <c r="W197">
         <v>4.2416228571428576</v>
       </c>
-      <c r="X197">
+      <c r="Y197">
         <v>17.2</v>
       </c>
     </row>
-    <row r="198" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>24</v>
       </c>
@@ -39289,6 +40695,9 @@
       <c r="I198" t="s">
         <v>15</v>
       </c>
+      <c r="J198" t="s">
+        <v>19</v>
+      </c>
       <c r="K198" t="s">
         <v>20</v>
       </c>
@@ -39325,11 +40734,11 @@
       <c r="W198">
         <v>7.5466285714285721</v>
       </c>
-      <c r="X198">
+      <c r="Y198">
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="199" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>25</v>
       </c>
@@ -39357,6 +40766,9 @@
       <c r="I199" t="s">
         <v>15</v>
       </c>
+      <c r="J199" t="s">
+        <v>19</v>
+      </c>
       <c r="K199" t="s">
         <v>20</v>
       </c>
@@ -39393,11 +40805,11 @@
       <c r="W199">
         <v>6.7056000000000013</v>
       </c>
-      <c r="X199">
+      <c r="Y199">
         <v>88.65</v>
       </c>
     </row>
-    <row r="200" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>25</v>
       </c>
@@ -39425,6 +40837,9 @@
       <c r="I200" t="s">
         <v>15</v>
       </c>
+      <c r="J200" t="s">
+        <v>19</v>
+      </c>
       <c r="K200" t="s">
         <v>20</v>
       </c>
@@ -39461,11 +40876,11 @@
       <c r="W200">
         <v>6.0800571428571422</v>
       </c>
-      <c r="X200">
+      <c r="Y200">
         <v>53.95</v>
       </c>
     </row>
-    <row r="201" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>24</v>
       </c>
@@ -39493,6 +40908,9 @@
       <c r="I201" t="s">
         <v>15</v>
       </c>
+      <c r="J201" t="s">
+        <v>19</v>
+      </c>
       <c r="K201" t="s">
         <v>20</v>
       </c>
@@ -39529,11 +40947,11 @@
       <c r="W201">
         <v>7.419428571428571</v>
       </c>
-      <c r="X201">
+      <c r="Y201">
         <v>133.6</v>
       </c>
     </row>
-    <row r="202" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>26</v>
       </c>
@@ -39561,6 +40979,9 @@
       <c r="I202" t="s">
         <v>15</v>
       </c>
+      <c r="J202" t="s">
+        <v>19</v>
+      </c>
       <c r="K202" t="s">
         <v>20</v>
       </c>
@@ -39597,11 +41018,11 @@
       <c r="W202">
         <v>3.2692114285714284</v>
       </c>
-      <c r="X202">
+      <c r="Y202">
         <v>25.6</v>
       </c>
     </row>
-    <row r="203" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>26</v>
       </c>
@@ -39629,6 +41050,9 @@
       <c r="I203" t="s">
         <v>15</v>
       </c>
+      <c r="J203" t="s">
+        <v>19</v>
+      </c>
       <c r="K203" t="s">
         <v>18</v>
       </c>
@@ -39647,11 +41071,11 @@
       <c r="Q203">
         <v>10</v>
       </c>
-      <c r="X203">
+      <c r="Y203">
         <v>50</v>
       </c>
     </row>
-    <row r="204" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>25</v>
       </c>
@@ -39679,6 +41103,9 @@
       <c r="I204" t="s">
         <v>15</v>
       </c>
+      <c r="J204" t="s">
+        <v>19</v>
+      </c>
       <c r="K204" t="s">
         <v>18</v>
       </c>
@@ -39697,11 +41124,11 @@
       <c r="Q204">
         <v>75.2</v>
       </c>
-      <c r="X204">
+      <c r="Y204">
         <v>148.9</v>
       </c>
     </row>
-    <row r="205" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>24</v>
       </c>
@@ -39729,6 +41156,9 @@
       <c r="I205" t="s">
         <v>15</v>
       </c>
+      <c r="J205" t="s">
+        <v>19</v>
+      </c>
       <c r="K205" t="s">
         <v>18</v>
       </c>
@@ -39747,11 +41177,11 @@
       <c r="Q205">
         <v>175.2</v>
       </c>
-      <c r="X205">
+      <c r="Y205">
         <v>93.8</v>
       </c>
     </row>
-    <row r="206" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>26</v>
       </c>
@@ -39779,6 +41209,9 @@
       <c r="I206" t="s">
         <v>15</v>
       </c>
+      <c r="J206" t="s">
+        <v>19</v>
+      </c>
       <c r="K206" t="s">
         <v>19</v>
       </c>
@@ -39815,11 +41248,11 @@
       <c r="W206">
         <v>5.701306496624623</v>
       </c>
-      <c r="X206">
+      <c r="Y206">
         <v>81.849999999999994</v>
       </c>
     </row>
-    <row r="207" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>25</v>
       </c>
@@ -39847,6 +41280,9 @@
       <c r="I207" t="s">
         <v>15</v>
       </c>
+      <c r="J207" t="s">
+        <v>19</v>
+      </c>
       <c r="K207" t="s">
         <v>19</v>
       </c>
@@ -39883,11 +41319,11 @@
       <c r="W207">
         <v>1.1185702143903604</v>
       </c>
-      <c r="X207">
+      <c r="Y207">
         <v>88.1</v>
       </c>
     </row>
-    <row r="208" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>24</v>
       </c>
@@ -39915,6 +41351,9 @@
       <c r="I208" t="s">
         <v>15</v>
       </c>
+      <c r="J208" t="s">
+        <v>19</v>
+      </c>
       <c r="K208" t="s">
         <v>19</v>
       </c>
@@ -39951,11 +41390,11 @@
       <c r="W208">
         <v>0.67330839099190742</v>
       </c>
-      <c r="X208">
+      <c r="Y208">
         <v>128.85</v>
       </c>
     </row>
-    <row r="209" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>24</v>
       </c>
@@ -39983,6 +41422,9 @@
       <c r="I209" t="s">
         <v>15</v>
       </c>
+      <c r="J209" t="s">
+        <v>19</v>
+      </c>
       <c r="K209" t="s">
         <v>17</v>
       </c>
@@ -40013,11 +41455,11 @@
       <c r="W209">
         <v>0</v>
       </c>
-      <c r="X209">
+      <c r="Y209">
         <v>46.400000000000006</v>
       </c>
     </row>
-    <row r="210" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>25</v>
       </c>
@@ -40045,6 +41487,9 @@
       <c r="I210" t="s">
         <v>15</v>
       </c>
+      <c r="J210" t="s">
+        <v>19</v>
+      </c>
       <c r="K210" t="s">
         <v>17</v>
       </c>
@@ -40075,11 +41520,11 @@
       <c r="W210">
         <v>0</v>
       </c>
-      <c r="X210">
+      <c r="Y210">
         <v>44.75</v>
       </c>
     </row>
-    <row r="211" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>26</v>
       </c>
@@ -40107,6 +41552,9 @@
       <c r="I211" t="s">
         <v>15</v>
       </c>
+      <c r="J211" t="s">
+        <v>19</v>
+      </c>
       <c r="K211" t="s">
         <v>17</v>
       </c>
@@ -40137,11 +41585,11 @@
       <c r="W211">
         <v>0</v>
       </c>
-      <c r="X211">
+      <c r="Y211">
         <v>37.1</v>
       </c>
     </row>
-    <row r="212" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>24</v>
       </c>
@@ -40169,6 +41617,9 @@
       <c r="I212" t="s">
         <v>15</v>
       </c>
+      <c r="J212" t="s">
+        <v>19</v>
+      </c>
       <c r="K212" t="s">
         <v>19</v>
       </c>
@@ -40205,11 +41656,11 @@
       <c r="W212">
         <v>0.75638122074206759</v>
       </c>
-      <c r="X212">
+      <c r="Y212">
         <v>129.35</v>
       </c>
     </row>
-    <row r="213" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>26</v>
       </c>
@@ -40237,6 +41688,9 @@
       <c r="I213" t="s">
         <v>15</v>
       </c>
+      <c r="J213" t="s">
+        <v>19</v>
+      </c>
       <c r="K213" t="s">
         <v>19</v>
       </c>
@@ -40273,11 +41727,11 @@
       <c r="W213">
         <v>6.867760091049405</v>
       </c>
-      <c r="X213">
+      <c r="Y213">
         <v>55.45</v>
       </c>
     </row>
-    <row r="214" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>25</v>
       </c>
@@ -40305,6 +41759,9 @@
       <c r="I214" t="s">
         <v>15</v>
       </c>
+      <c r="J214" t="s">
+        <v>19</v>
+      </c>
       <c r="K214" t="s">
         <v>19</v>
       </c>
@@ -40341,11 +41798,11 @@
       <c r="W214">
         <v>1.3176069325801945</v>
       </c>
-      <c r="X214">
+      <c r="Y214">
         <v>107.05</v>
       </c>
     </row>
-    <row r="215" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>25</v>
       </c>
@@ -40373,6 +41830,9 @@
       <c r="I215" t="s">
         <v>15</v>
       </c>
+      <c r="J215" t="s">
+        <v>19</v>
+      </c>
       <c r="K215" t="s">
         <v>20</v>
       </c>
@@ -40409,11 +41869,11 @@
       <c r="W215">
         <v>7.2065772594752175</v>
       </c>
-      <c r="X215">
+      <c r="Y215">
         <v>94.95</v>
       </c>
     </row>
-    <row r="216" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>24</v>
       </c>
@@ -40441,6 +41901,9 @@
       <c r="I216" t="s">
         <v>15</v>
       </c>
+      <c r="J216" t="s">
+        <v>19</v>
+      </c>
       <c r="K216" t="s">
         <v>20</v>
       </c>
@@ -40477,11 +41940,11 @@
       <c r="W216">
         <v>8.6074169096209889</v>
       </c>
-      <c r="X216">
+      <c r="Y216">
         <v>102.4</v>
       </c>
     </row>
-    <row r="217" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>26</v>
       </c>
@@ -40509,6 +41972,9 @@
       <c r="I217" t="s">
         <v>15</v>
       </c>
+      <c r="J217" t="s">
+        <v>19</v>
+      </c>
       <c r="K217" t="s">
         <v>20</v>
       </c>
@@ -40545,11 +42011,11 @@
       <c r="W217">
         <v>4.1901807580174921</v>
       </c>
-      <c r="X217">
+      <c r="Y217">
         <v>53.95</v>
       </c>
     </row>
-    <row r="218" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>26</v>
       </c>
@@ -40577,6 +42043,9 @@
       <c r="I218" t="s">
         <v>15</v>
       </c>
+      <c r="J218" t="s">
+        <v>19</v>
+      </c>
       <c r="K218" t="s">
         <v>18</v>
       </c>
@@ -40613,11 +42082,11 @@
       <c r="W218">
         <v>4.451485714285714</v>
       </c>
-      <c r="X218">
+      <c r="Y218">
         <v>95</v>
       </c>
     </row>
-    <row r="219" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>24</v>
       </c>
@@ -40645,6 +42114,9 @@
       <c r="I219" t="s">
         <v>15</v>
       </c>
+      <c r="J219" t="s">
+        <v>19</v>
+      </c>
       <c r="K219" t="s">
         <v>18</v>
       </c>
@@ -40681,11 +42153,11 @@
       <c r="W219">
         <v>0.55303326810176123</v>
       </c>
-      <c r="X219">
+      <c r="Y219">
         <v>98.35</v>
       </c>
     </row>
-    <row r="220" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>25</v>
       </c>
@@ -40713,6 +42185,9 @@
       <c r="I220" t="s">
         <v>15</v>
       </c>
+      <c r="J220" t="s">
+        <v>19</v>
+      </c>
       <c r="K220" t="s">
         <v>18</v>
       </c>
@@ -40749,11 +42224,11 @@
       <c r="W220">
         <v>0.98640273556231006</v>
       </c>
-      <c r="X220">
+      <c r="Y220">
         <v>45.3</v>
       </c>
     </row>
-    <row r="221" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>26</v>
       </c>
@@ -40781,6 +42256,9 @@
       <c r="I221" t="s">
         <v>15</v>
       </c>
+      <c r="J221" t="s">
+        <v>19</v>
+      </c>
       <c r="K221" t="s">
         <v>18</v>
       </c>
@@ -40814,11 +42292,11 @@
       <c r="W221">
         <v>3.6460311173974547</v>
       </c>
-      <c r="X221">
+      <c r="Y221">
         <v>25.85</v>
       </c>
     </row>
-    <row r="222" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>25</v>
       </c>
@@ -40846,6 +42324,9 @@
       <c r="I222" t="s">
         <v>15</v>
       </c>
+      <c r="J222" t="s">
+        <v>19</v>
+      </c>
       <c r="K222" t="s">
         <v>18</v>
       </c>
@@ -40879,11 +42360,11 @@
       <c r="W222">
         <v>0.78533208943994703</v>
       </c>
-      <c r="X222">
+      <c r="Y222">
         <v>28.55</v>
       </c>
     </row>
-    <row r="223" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>24</v>
       </c>
@@ -40911,6 +42392,9 @@
       <c r="I223" t="s">
         <v>15</v>
       </c>
+      <c r="J223" t="s">
+        <v>19</v>
+      </c>
       <c r="K223" t="s">
         <v>18</v>
       </c>
@@ -40944,11 +42428,11 @@
       <c r="W223">
         <v>0.41679745273940311</v>
       </c>
-      <c r="X223">
+      <c r="Y223">
         <v>136.89999999999998</v>
       </c>
     </row>
-    <row r="224" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>24</v>
       </c>
@@ -40976,6 +42460,9 @@
       <c r="I224" t="s">
         <v>15</v>
       </c>
+      <c r="J224" t="s">
+        <v>19</v>
+      </c>
       <c r="K224" t="s">
         <v>17</v>
       </c>
@@ -41006,11 +42493,11 @@
       <c r="W224">
         <v>0</v>
       </c>
-      <c r="X224">
+      <c r="Y224">
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="225" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>25</v>
       </c>
@@ -41038,6 +42525,9 @@
       <c r="I225" t="s">
         <v>15</v>
       </c>
+      <c r="J225" t="s">
+        <v>19</v>
+      </c>
       <c r="K225" t="s">
         <v>17</v>
       </c>
@@ -41068,11 +42558,11 @@
       <c r="W225">
         <v>0</v>
       </c>
-      <c r="X225">
+      <c r="Y225">
         <v>46.75</v>
       </c>
     </row>
-    <row r="226" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>26</v>
       </c>
@@ -41100,6 +42590,9 @@
       <c r="I226" t="s">
         <v>15</v>
       </c>
+      <c r="J226" t="s">
+        <v>19</v>
+      </c>
       <c r="K226" t="s">
         <v>17</v>
       </c>
@@ -41130,11 +42623,11 @@
       <c r="W226">
         <v>0</v>
       </c>
-      <c r="X226">
+      <c r="Y226">
         <v>84.35</v>
       </c>
     </row>
-    <row r="227" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>25</v>
       </c>
@@ -41162,6 +42655,9 @@
       <c r="I227" t="s">
         <v>15</v>
       </c>
+      <c r="J227" t="s">
+        <v>19</v>
+      </c>
       <c r="K227" t="s">
         <v>17</v>
       </c>
@@ -41198,11 +42694,11 @@
       <c r="W227">
         <v>0.73851379632312708</v>
       </c>
-      <c r="X227">
+      <c r="Y227">
         <v>120.35</v>
       </c>
     </row>
-    <row r="228" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>26</v>
       </c>
@@ -41230,6 +42726,9 @@
       <c r="I228" t="s">
         <v>15</v>
       </c>
+      <c r="J228" t="s">
+        <v>19</v>
+      </c>
       <c r="K228" t="s">
         <v>17</v>
       </c>
@@ -41266,11 +42765,11 @@
       <c r="W228">
         <v>4.189896648314499</v>
       </c>
-      <c r="X228">
+      <c r="Y228">
         <v>80.3</v>
       </c>
     </row>
-    <row r="229" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>24</v>
       </c>
@@ -41298,6 +42797,9 @@
       <c r="I229" t="s">
         <v>15</v>
       </c>
+      <c r="J229" t="s">
+        <v>19</v>
+      </c>
       <c r="K229" t="s">
         <v>17</v>
       </c>
@@ -41334,11 +42836,11 @@
       <c r="W229">
         <v>0.51229723456909548</v>
       </c>
-      <c r="X229">
+      <c r="Y229">
         <v>90.05</v>
       </c>
     </row>
-    <row r="230" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>24</v>
       </c>
@@ -41366,6 +42868,9 @@
       <c r="I230" t="s">
         <v>15</v>
       </c>
+      <c r="J230" t="s">
+        <v>19</v>
+      </c>
       <c r="K230" t="s">
         <v>19</v>
       </c>
@@ -41384,11 +42889,11 @@
       <c r="Q230">
         <v>175.2</v>
       </c>
-      <c r="X230">
+      <c r="Y230">
         <v>146.15</v>
       </c>
     </row>
-    <row r="231" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>26</v>
       </c>
@@ -41416,6 +42921,9 @@
       <c r="I231" t="s">
         <v>15</v>
       </c>
+      <c r="J231" t="s">
+        <v>19</v>
+      </c>
       <c r="K231" t="s">
         <v>19</v>
       </c>
@@ -41434,11 +42942,11 @@
       <c r="Q231">
         <v>10</v>
       </c>
-      <c r="X231">
+      <c r="Y231">
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="232" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>25</v>
       </c>
@@ -41466,6 +42974,9 @@
       <c r="I232" t="s">
         <v>15</v>
       </c>
+      <c r="J232" t="s">
+        <v>19</v>
+      </c>
       <c r="K232" t="s">
         <v>19</v>
       </c>
@@ -41484,11 +42995,11 @@
       <c r="Q232">
         <v>75.2</v>
       </c>
-      <c r="X232">
+      <c r="Y232">
         <v>151.65</v>
       </c>
     </row>
-    <row r="233" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>25</v>
       </c>
@@ -41516,6 +43027,9 @@
       <c r="I233" t="s">
         <v>15</v>
       </c>
+      <c r="J233" t="s">
+        <v>19</v>
+      </c>
       <c r="K233" t="s">
         <v>18</v>
       </c>
@@ -41546,11 +43060,11 @@
       <c r="W233">
         <v>0</v>
       </c>
-      <c r="X233">
+      <c r="Y233">
         <v>48.1</v>
       </c>
     </row>
-    <row r="234" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>26</v>
       </c>
@@ -41578,6 +43092,9 @@
       <c r="I234" t="s">
         <v>15</v>
       </c>
+      <c r="J234" t="s">
+        <v>19</v>
+      </c>
       <c r="K234" t="s">
         <v>18</v>
       </c>
@@ -41608,11 +43125,11 @@
       <c r="W234">
         <v>0</v>
       </c>
-      <c r="X234">
+      <c r="Y234">
         <v>24.85</v>
       </c>
     </row>
-    <row r="235" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>24</v>
       </c>
@@ -41640,6 +43157,9 @@
       <c r="I235" t="s">
         <v>15</v>
       </c>
+      <c r="J235" t="s">
+        <v>19</v>
+      </c>
       <c r="K235" t="s">
         <v>18</v>
       </c>
@@ -41670,11 +43190,11 @@
       <c r="W235">
         <v>0</v>
       </c>
-      <c r="X235">
+      <c r="Y235">
         <v>77.95</v>
       </c>
     </row>
-    <row r="236" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>26</v>
       </c>
@@ -41702,6 +43222,9 @@
       <c r="I236" t="s">
         <v>15</v>
       </c>
+      <c r="J236" t="s">
+        <v>19</v>
+      </c>
       <c r="K236" t="s">
         <v>20</v>
       </c>
@@ -41735,11 +43258,11 @@
       <c r="W236">
         <v>3.6169600000000002</v>
       </c>
-      <c r="X236">
+      <c r="Y236">
         <v>34.6</v>
       </c>
     </row>
-    <row r="237" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>24</v>
       </c>
@@ -41767,6 +43290,9 @@
       <c r="I237" t="s">
         <v>15</v>
       </c>
+      <c r="J237" t="s">
+        <v>19</v>
+      </c>
       <c r="K237" t="s">
         <v>20</v>
       </c>
@@ -41800,11 +43326,11 @@
       <c r="W237">
         <v>5.9222399999999995</v>
       </c>
-      <c r="X237">
+      <c r="Y237">
         <v>69.25</v>
       </c>
     </row>
-    <row r="238" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>25</v>
       </c>
@@ -41832,6 +43358,9 @@
       <c r="I238" t="s">
         <v>15</v>
       </c>
+      <c r="J238" t="s">
+        <v>19</v>
+      </c>
       <c r="K238" t="s">
         <v>20</v>
       </c>
@@ -41865,11 +43394,11 @@
       <c r="W238">
         <v>3.9980571428571432</v>
       </c>
-      <c r="X238">
+      <c r="Y238">
         <v>40.450000000000003</v>
       </c>
     </row>
-    <row r="239" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>25</v>
       </c>
@@ -41897,6 +43426,9 @@
       <c r="I239" t="s">
         <v>15</v>
       </c>
+      <c r="J239" t="s">
+        <v>19</v>
+      </c>
       <c r="K239" t="s">
         <v>17</v>
       </c>
@@ -41933,11 +43465,11 @@
       <c r="W239">
         <v>0.84039157534935138</v>
       </c>
-      <c r="X239">
+      <c r="Y239">
         <v>103.7</v>
       </c>
     </row>
-    <row r="240" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>24</v>
       </c>
@@ -41965,6 +43497,9 @@
       <c r="I240" t="s">
         <v>15</v>
       </c>
+      <c r="J240" t="s">
+        <v>19</v>
+      </c>
       <c r="K240" t="s">
         <v>17</v>
       </c>
@@ -42001,11 +43536,11 @@
       <c r="W240">
         <v>0.47852111402471403</v>
       </c>
-      <c r="X240">
+      <c r="Y240">
         <v>67.55</v>
       </c>
     </row>
-    <row r="241" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>26</v>
       </c>
@@ -42033,6 +43568,9 @@
       <c r="I241" t="s">
         <v>15</v>
       </c>
+      <c r="J241" t="s">
+        <v>19</v>
+      </c>
       <c r="K241" t="s">
         <v>17</v>
       </c>
@@ -42069,11 +43607,11 @@
       <c r="W241">
         <v>3.5330752990851506</v>
       </c>
-      <c r="X241">
+      <c r="Y241">
         <v>44.4</v>
       </c>
     </row>
-    <row r="242" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>26</v>
       </c>
@@ -42101,6 +43639,9 @@
       <c r="I242" t="s">
         <v>15</v>
       </c>
+      <c r="J242" t="s">
+        <v>19</v>
+      </c>
       <c r="K242" t="s">
         <v>19</v>
       </c>
@@ -42134,11 +43675,11 @@
       <c r="W242">
         <v>2.1991541714725105</v>
       </c>
-      <c r="X242">
+      <c r="Y242">
         <v>22.799999999999997</v>
       </c>
     </row>
-    <row r="243" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>25</v>
       </c>
@@ -42166,6 +43707,9 @@
       <c r="I243" t="s">
         <v>15</v>
       </c>
+      <c r="J243" t="s">
+        <v>19</v>
+      </c>
       <c r="K243" t="s">
         <v>19</v>
       </c>
@@ -42199,11 +43743,11 @@
       <c r="W243">
         <v>0.84135366456851202</v>
       </c>
-      <c r="X243">
+      <c r="Y243">
         <v>94</v>
       </c>
     </row>
-    <row r="244" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>24</v>
       </c>
@@ -42231,6 +43775,9 @@
       <c r="I244" t="s">
         <v>15</v>
       </c>
+      <c r="J244" t="s">
+        <v>19</v>
+      </c>
       <c r="K244" t="s">
         <v>19</v>
       </c>
@@ -42264,11 +43811,11 @@
       <c r="W244">
         <v>0.53576446416514789</v>
       </c>
-      <c r="X244">
+      <c r="Y244">
         <v>99.85</v>
       </c>
     </row>
-    <row r="245" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>25</v>
       </c>
@@ -42296,6 +43843,9 @@
       <c r="I245" t="s">
         <v>15</v>
       </c>
+      <c r="J245" t="s">
+        <v>19</v>
+      </c>
       <c r="K245" t="s">
         <v>17</v>
       </c>
@@ -42332,11 +43882,11 @@
       <c r="W245">
         <v>0.97041536050156729</v>
       </c>
-      <c r="X245">
+      <c r="Y245">
         <v>88.25</v>
       </c>
     </row>
-    <row r="246" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>24</v>
       </c>
@@ -42364,6 +43914,9 @@
       <c r="I246" t="s">
         <v>15</v>
       </c>
+      <c r="J246" t="s">
+        <v>19</v>
+      </c>
       <c r="K246" t="s">
         <v>17</v>
       </c>
@@ -42400,11 +43953,11 @@
       <c r="W246">
         <v>0.69614975099903642</v>
       </c>
-      <c r="X246">
+      <c r="Y246">
         <v>97.2</v>
       </c>
     </row>
-    <row r="247" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>26</v>
       </c>
@@ -42432,6 +43985,9 @@
       <c r="I247" t="s">
         <v>15</v>
       </c>
+      <c r="J247" t="s">
+        <v>19</v>
+      </c>
       <c r="K247" t="s">
         <v>17</v>
       </c>
@@ -42468,11 +44024,11 @@
       <c r="W247">
         <v>6.6258128078817737</v>
       </c>
-      <c r="X247">
+      <c r="Y247">
         <v>56.849999999999994</v>
       </c>
     </row>
-    <row r="248" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>24</v>
       </c>
@@ -42500,6 +44056,9 @@
       <c r="I248" t="s">
         <v>15</v>
       </c>
+      <c r="J248" t="s">
+        <v>19</v>
+      </c>
       <c r="K248" t="s">
         <v>17</v>
       </c>
@@ -42536,11 +44095,11 @@
       <c r="W248">
         <v>0.4692135073756849</v>
       </c>
-      <c r="X248">
+      <c r="Y248">
         <v>90.25</v>
       </c>
     </row>
-    <row r="249" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>26</v>
       </c>
@@ -42568,6 +44127,9 @@
       <c r="I249" t="s">
         <v>15</v>
       </c>
+      <c r="J249" t="s">
+        <v>19</v>
+      </c>
       <c r="K249" t="s">
         <v>17</v>
       </c>
@@ -42604,11 +44166,11 @@
       <c r="W249">
         <v>3.7932635467980296</v>
       </c>
-      <c r="X249">
+      <c r="Y249">
         <v>25.85</v>
       </c>
     </row>
-    <row r="250" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>25</v>
       </c>
@@ -42636,6 +44198,9 @@
       <c r="I250" t="s">
         <v>15</v>
       </c>
+      <c r="J250" t="s">
+        <v>19</v>
+      </c>
       <c r="K250" t="s">
         <v>17</v>
       </c>
@@ -42672,11 +44237,11 @@
       <c r="W250">
         <v>0.66703674677812608</v>
       </c>
-      <c r="X250">
+      <c r="Y250">
         <v>17.95</v>
       </c>
     </row>
-    <row r="251" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>26</v>
       </c>
@@ -42704,6 +44269,9 @@
       <c r="I251" t="s">
         <v>15</v>
       </c>
+      <c r="J251" t="s">
+        <v>19</v>
+      </c>
       <c r="K251" t="s">
         <v>20</v>
       </c>
@@ -42737,11 +44305,11 @@
       <c r="W251">
         <v>3.8285942857142841</v>
       </c>
-      <c r="X251">
+      <c r="Y251">
         <v>94.05</v>
       </c>
     </row>
-    <row r="252" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>24</v>
       </c>
@@ -42769,6 +44337,9 @@
       <c r="I252" t="s">
         <v>15</v>
       </c>
+      <c r="J252" t="s">
+        <v>19</v>
+      </c>
       <c r="K252" t="s">
         <v>20</v>
       </c>
@@ -42802,11 +44373,11 @@
       <c r="W252">
         <v>9.2775428571428584</v>
       </c>
-      <c r="X252">
+      <c r="Y252">
         <v>205.35</v>
       </c>
     </row>
-    <row r="253" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>25</v>
       </c>
@@ -42834,6 +44405,9 @@
       <c r="I253" t="s">
         <v>15</v>
       </c>
+      <c r="J253" t="s">
+        <v>19</v>
+      </c>
       <c r="K253" t="s">
         <v>20</v>
       </c>
@@ -42867,11 +44441,11 @@
       <c r="W253">
         <v>7.0152000000000001</v>
       </c>
-      <c r="X253">
+      <c r="Y253">
         <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="254" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>24</v>
       </c>
@@ -42899,6 +44473,9 @@
       <c r="I254" t="s">
         <v>15</v>
       </c>
+      <c r="J254" t="s">
+        <v>19</v>
+      </c>
       <c r="K254" t="s">
         <v>18</v>
       </c>
@@ -42935,11 +44512,11 @@
       <c r="W254">
         <v>0.36752120026092633</v>
       </c>
-      <c r="X254">
+      <c r="Y254">
         <v>86.449999999999989</v>
       </c>
     </row>
-    <row r="255" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>25</v>
       </c>
@@ -42967,6 +44544,9 @@
       <c r="I255" t="s">
         <v>15</v>
       </c>
+      <c r="J255" t="s">
+        <v>19</v>
+      </c>
       <c r="K255" t="s">
         <v>18</v>
       </c>
@@ -43003,11 +44583,11 @@
       <c r="W255">
         <v>0.74642857142857144</v>
       </c>
-      <c r="X255">
+      <c r="Y255">
         <v>37.599999999999994</v>
       </c>
     </row>
-    <row r="256" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>26</v>
       </c>
@@ -43035,6 +44615,9 @@
       <c r="I256" t="s">
         <v>15</v>
       </c>
+      <c r="J256" t="s">
+        <v>19</v>
+      </c>
       <c r="K256" t="s">
         <v>18</v>
       </c>
@@ -43071,11 +44654,11 @@
       <c r="W256">
         <v>2.6830857142857143</v>
       </c>
-      <c r="X256">
+      <c r="Y256">
         <v>39.9</v>
       </c>
     </row>
-    <row r="257" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>24</v>
       </c>
@@ -43103,6 +44686,9 @@
       <c r="I257" t="s">
         <v>15</v>
       </c>
+      <c r="J257" t="s">
+        <v>19</v>
+      </c>
       <c r="K257" t="s">
         <v>18</v>
       </c>
@@ -43139,11 +44725,11 @@
       <c r="W257">
         <v>0.50081800391389442</v>
       </c>
-      <c r="X257">
+      <c r="Y257">
         <v>72.150000000000006</v>
       </c>
     </row>
-    <row r="258" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>26</v>
       </c>
@@ -43171,6 +44757,9 @@
       <c r="I258" t="s">
         <v>15</v>
       </c>
+      <c r="J258" t="s">
+        <v>19</v>
+      </c>
       <c r="K258" t="s">
         <v>18</v>
       </c>
@@ -43207,11 +44796,11 @@
       <c r="W258">
         <v>4.0548571428571432</v>
       </c>
-      <c r="X258">
+      <c r="Y258">
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="259" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>25</v>
       </c>
@@ -43239,6 +44828,9 @@
       <c r="I259" t="s">
         <v>15</v>
       </c>
+      <c r="J259" t="s">
+        <v>19</v>
+      </c>
       <c r="K259" t="s">
         <v>18</v>
       </c>
@@ -43275,11 +44867,11 @@
       <c r="W259">
         <v>0.93118541033434643</v>
       </c>
-      <c r="X259">
+      <c r="Y259">
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="260" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>26</v>
       </c>
@@ -43307,6 +44899,9 @@
       <c r="I260" t="s">
         <v>15</v>
       </c>
+      <c r="J260" t="s">
+        <v>19</v>
+      </c>
       <c r="K260" t="s">
         <v>19</v>
       </c>
@@ -43343,11 +44938,11 @@
       <c r="W260">
         <v>2.3465749936338165</v>
       </c>
-      <c r="X260">
+      <c r="Y260">
         <v>60.6</v>
       </c>
     </row>
-    <row r="261" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>25</v>
       </c>
@@ -43375,6 +44970,9 @@
       <c r="I261" t="s">
         <v>15</v>
       </c>
+      <c r="J261" t="s">
+        <v>19</v>
+      </c>
       <c r="K261" t="s">
         <v>19</v>
       </c>
@@ -43411,11 +45009,11 @@
       <c r="W261">
         <v>0.35447259711965595</v>
       </c>
-      <c r="X261">
+      <c r="Y261">
         <v>121.1</v>
       </c>
     </row>
-    <row r="262" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>24</v>
       </c>
@@ -43443,6 +45041,9 @@
       <c r="I262" t="s">
         <v>15</v>
       </c>
+      <c r="J262" t="s">
+        <v>19</v>
+      </c>
       <c r="K262" t="s">
         <v>19</v>
       </c>
@@ -43479,11 +45080,11 @@
       <c r="W262">
         <v>0.26027324248938472</v>
       </c>
-      <c r="X262">
+      <c r="Y262">
         <v>53.85</v>
       </c>
     </row>
-    <row r="263" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>25</v>
       </c>
@@ -43511,6 +45112,9 @@
       <c r="I263" t="s">
         <v>15</v>
       </c>
+      <c r="J263" t="s">
+        <v>19</v>
+      </c>
       <c r="K263" t="s">
         <v>18</v>
       </c>
@@ -43529,11 +45133,11 @@
       <c r="Q263">
         <v>75.2</v>
       </c>
-      <c r="X263">
+      <c r="Y263">
         <v>67.900000000000006</v>
       </c>
     </row>
-    <row r="264" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>24</v>
       </c>
@@ -43561,6 +45165,9 @@
       <c r="I264" t="s">
         <v>15</v>
       </c>
+      <c r="J264" t="s">
+        <v>19</v>
+      </c>
       <c r="K264" t="s">
         <v>18</v>
       </c>
@@ -43579,11 +45186,11 @@
       <c r="Q264">
         <v>175.2</v>
       </c>
-      <c r="X264">
+      <c r="Y264">
         <v>100.05</v>
       </c>
     </row>
-    <row r="265" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>26</v>
       </c>
@@ -43611,6 +45218,9 @@
       <c r="I265" t="s">
         <v>15</v>
       </c>
+      <c r="J265" t="s">
+        <v>19</v>
+      </c>
       <c r="K265" t="s">
         <v>18</v>
       </c>
@@ -43629,11 +45239,11 @@
       <c r="Q265">
         <v>10</v>
       </c>
-      <c r="X265">
+      <c r="Y265">
         <v>39.9</v>
       </c>
     </row>
-    <row r="266" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>24</v>
       </c>
@@ -43661,6 +45271,9 @@
       <c r="I266" t="s">
         <v>15</v>
       </c>
+      <c r="J266" t="s">
+        <v>19</v>
+      </c>
       <c r="K266" t="s">
         <v>17</v>
       </c>
@@ -43691,11 +45304,11 @@
       <c r="W266">
         <v>0</v>
       </c>
-      <c r="X266">
+      <c r="Y266">
         <v>62</v>
       </c>
     </row>
-    <row r="267" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>25</v>
       </c>
@@ -43723,6 +45336,9 @@
       <c r="I267" t="s">
         <v>15</v>
       </c>
+      <c r="J267" t="s">
+        <v>19</v>
+      </c>
       <c r="K267" t="s">
         <v>17</v>
       </c>
@@ -43753,11 +45369,11 @@
       <c r="W267">
         <v>0</v>
       </c>
-      <c r="X267">
+      <c r="Y267">
         <v>49.65</v>
       </c>
     </row>
-    <row r="268" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>26</v>
       </c>
@@ -43785,6 +45401,9 @@
       <c r="I268" t="s">
         <v>15</v>
       </c>
+      <c r="J268" t="s">
+        <v>19</v>
+      </c>
       <c r="K268" t="s">
         <v>17</v>
       </c>
@@ -43815,11 +45434,11 @@
       <c r="W268">
         <v>0</v>
       </c>
-      <c r="X268">
+      <c r="Y268">
         <v>31.25</v>
       </c>
     </row>
-    <row r="269" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>25</v>
       </c>
@@ -43847,6 +45466,9 @@
       <c r="I269" t="s">
         <v>15</v>
       </c>
+      <c r="J269" t="s">
+        <v>19</v>
+      </c>
       <c r="K269" t="s">
         <v>20</v>
       </c>
@@ -43883,11 +45505,11 @@
       <c r="W269">
         <v>4.9472186588921279</v>
       </c>
-      <c r="X269">
+      <c r="Y269">
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="270" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>24</v>
       </c>
@@ -43915,6 +45537,9 @@
       <c r="I270" t="s">
         <v>15</v>
       </c>
+      <c r="J270" t="s">
+        <v>19</v>
+      </c>
       <c r="K270" t="s">
         <v>20</v>
       </c>
@@ -43951,11 +45576,11 @@
       <c r="W270">
         <v>4.5008629737609329</v>
       </c>
-      <c r="X270">
+      <c r="Y270">
         <v>51.55</v>
       </c>
     </row>
-    <row r="271" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>26</v>
       </c>
@@ -43983,6 +45608,9 @@
       <c r="I271" t="s">
         <v>15</v>
       </c>
+      <c r="J271" t="s">
+        <v>19</v>
+      </c>
       <c r="K271" t="s">
         <v>20</v>
       </c>
@@ -44019,7 +45647,7 @@
       <c r="W271">
         <v>1.6436151603498543</v>
       </c>
-      <c r="X271">
+      <c r="Y271">
         <v>20.549999999999997</v>
       </c>
     </row>

--- a/DataMaster.xlsx
+++ b/DataMaster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\young\Dropbox\Michael\Work-Uni-Coding\Youngs Farm Analysis\FOG\Work\R&amp;D\Stirlings to Coast\RiskWise\Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE20ADB-0E83-423F-AFDC-E8E3254FD922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E19A01-BD38-45C2-B0FB-35E87A231F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28950" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{10EDD844-9EC5-4F2C-A4A7-506A3C8B05B2}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{10EDD844-9EC5-4F2C-A4A7-506A3C8B05B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -26309,7 +26309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3321" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3327" uniqueCount="39">
   <si>
     <t>Year</t>
   </si>
@@ -41071,6 +41071,9 @@
       <c r="Q203">
         <v>10</v>
       </c>
+      <c r="R203" t="s">
+        <v>36</v>
+      </c>
       <c r="Y203">
         <v>50</v>
       </c>
@@ -41124,6 +41127,9 @@
       <c r="Q204">
         <v>75.2</v>
       </c>
+      <c r="R204" t="s">
+        <v>36</v>
+      </c>
       <c r="Y204">
         <v>148.9</v>
       </c>
@@ -41177,6 +41183,9 @@
       <c r="Q205">
         <v>175.2</v>
       </c>
+      <c r="R205" t="s">
+        <v>36</v>
+      </c>
       <c r="Y205">
         <v>93.8</v>
       </c>
@@ -43448,7 +43457,7 @@
         <v>79.2</v>
       </c>
       <c r="R239">
-        <v>4.2893586005830899</v>
+        <v>4.5151143164032534</v>
       </c>
       <c r="S239">
         <v>9</v>
@@ -43519,7 +43528,7 @@
         <v>146.19999999999999</v>
       </c>
       <c r="R240">
-        <v>4.0174927113702621</v>
+        <v>4.2289396961792232</v>
       </c>
       <c r="S240">
         <v>10.1</v>
@@ -43590,7 +43599,7 @@
         <v>10</v>
       </c>
       <c r="R241">
-        <v>2.4395043731778423</v>
+        <v>2.710560414642047</v>
       </c>
       <c r="S241">
         <v>8.4</v>
@@ -44078,7 +44087,7 @@
         <v>146.19999999999999</v>
       </c>
       <c r="R248">
-        <v>3.862857142857143</v>
+        <v>4.0661654135338345</v>
       </c>
       <c r="S248">
         <v>10.3</v>
@@ -44149,7 +44158,7 @@
         <v>10</v>
       </c>
       <c r="R249">
-        <v>2.6507142857142858</v>
+        <v>2.9452380952380954</v>
       </c>
       <c r="S249">
         <v>8.3000000000000007</v>
@@ -44220,7 +44229,7 @@
         <v>79.2</v>
       </c>
       <c r="R250">
-        <v>3.3671428571428574</v>
+        <v>3.7412698412698422</v>
       </c>
       <c r="S250">
         <v>9.1</v>
@@ -44495,7 +44504,7 @@
         <v>146.19999999999999</v>
       </c>
       <c r="R254">
-        <v>3.9071428571428566</v>
+        <v>4.3412698412698409</v>
       </c>
       <c r="S254">
         <v>10.3</v>
@@ -44566,7 +44575,7 @@
         <v>79.2</v>
       </c>
       <c r="R255">
-        <v>3.6928571428571426</v>
+        <v>4.1031746031746028</v>
       </c>
       <c r="S255">
         <v>9.5</v>
@@ -44637,7 +44646,7 @@
         <v>10</v>
       </c>
       <c r="R256">
-        <v>1.9728571428571429</v>
+        <v>2.1920634920634923</v>
       </c>
       <c r="S256">
         <v>8.5</v>
@@ -44708,7 +44717,7 @@
         <v>146.19999999999999</v>
       </c>
       <c r="R257">
-        <v>5.3764285714285718</v>
+        <v>5.6593984962406019</v>
       </c>
       <c r="S257">
         <v>10.199999999999999</v>
@@ -44779,7 +44788,7 @@
         <v>10</v>
       </c>
       <c r="R258">
-        <v>3.1678571428571427</v>
+        <v>3.3345864661654137</v>
       </c>
       <c r="S258">
         <v>8</v>
@@ -44850,7 +44859,7 @@
         <v>79.2</v>
       </c>
       <c r="R259">
-        <v>4.7571428571428571</v>
+        <v>5.0075187969924819</v>
       </c>
       <c r="S259">
         <v>9.1999999999999993</v>
@@ -44921,7 +44930,7 @@
         <v>10</v>
       </c>
       <c r="R260">
-        <v>1.357142857142857</v>
+        <v>1.5079365079365079</v>
       </c>
       <c r="S260">
         <v>9.6999999999999993</v>
@@ -44992,7 +45001,7 @@
         <v>79.2</v>
       </c>
       <c r="R261">
-        <v>1.6578571428571429</v>
+        <v>2.0723214285714286</v>
       </c>
       <c r="S261">
         <v>9.5</v>
@@ -45063,7 +45072,7 @@
         <v>146.19999999999999</v>
       </c>
       <c r="R262">
-        <v>2.092857142857143</v>
+        <v>2.46218487394958</v>
       </c>
       <c r="S262">
         <v>10.199999999999999</v>
@@ -45133,6 +45142,9 @@
       <c r="Q263">
         <v>75.2</v>
       </c>
+      <c r="R263" t="s">
+        <v>36</v>
+      </c>
       <c r="Y263">
         <v>67.900000000000006</v>
       </c>
@@ -45186,6 +45198,9 @@
       <c r="Q264">
         <v>175.2</v>
       </c>
+      <c r="R264" t="s">
+        <v>36</v>
+      </c>
       <c r="Y264">
         <v>100.05</v>
       </c>
@@ -45239,6 +45254,9 @@
       <c r="Q265">
         <v>10</v>
       </c>
+      <c r="R265" t="s">
+        <v>36</v>
+      </c>
       <c r="Y265">
         <v>39.9</v>
       </c>
@@ -45293,7 +45311,7 @@
         <v>10</v>
       </c>
       <c r="R266">
-        <v>2.0807142857142855</v>
+        <v>2.6008928571428571</v>
       </c>
       <c r="U266">
         <v>0</v>
@@ -45358,7 +45376,7 @@
         <v>10</v>
       </c>
       <c r="R267">
-        <v>2.6428571428571428</v>
+        <v>2.9365079365079367</v>
       </c>
       <c r="U267">
         <v>0</v>
@@ -45423,7 +45441,7 @@
         <v>10</v>
       </c>
       <c r="R268">
-        <v>2.2164285714285716</v>
+        <v>4.4328571428571433</v>
       </c>
       <c r="U268">
         <v>0</v>
@@ -45488,7 +45506,7 @@
         <v>79.2</v>
       </c>
       <c r="R269">
-        <v>3.2208454810495626</v>
+        <v>3.5787172011661799</v>
       </c>
       <c r="S269">
         <v>9.6</v>
@@ -45559,7 +45577,7 @@
         <v>146.19999999999999</v>
       </c>
       <c r="R270">
-        <v>2.629008746355685</v>
+        <v>3.5053449951409137</v>
       </c>
       <c r="S270">
         <v>10.7</v>
@@ -45630,7 +45648,7 @@
         <v>10</v>
       </c>
       <c r="R271">
-        <v>1.1413994169096211</v>
+        <v>2.2827988338192422</v>
       </c>
       <c r="S271">
         <v>9</v>
